--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="281">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -577,6 +577,15 @@
     <t>['12', '79']</t>
   </si>
   <si>
+    <t>['17', '83']</t>
+  </si>
+  <si>
+    <t>['23', '38', '74']</t>
+  </si>
+  <si>
+    <t>['23', '69']</t>
+  </si>
+  <si>
     <t>['12', '38', '90+11']</t>
   </si>
   <si>
@@ -842,6 +851,12 @@
   </si>
   <si>
     <t>['1', '8', '19']</t>
+  </si>
+  <si>
+    <t>['85', '90']</t>
+  </si>
+  <si>
+    <t>['32']</t>
   </si>
 </sst>
 </file>
@@ -1203,7 +1218,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP137"/>
+  <dimension ref="A1:BP142"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1459,7 +1474,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -1746,7 +1761,7 @@
         <v>2</v>
       </c>
       <c r="AQ3">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1871,7 +1886,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -1949,10 +1964,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ4">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2077,7 +2092,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2155,7 +2170,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ5">
         <v>1.29</v>
@@ -2283,7 +2298,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2489,7 +2504,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2567,10 +2582,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ7">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2776,7 +2791,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ8">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2901,7 +2916,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3107,7 +3122,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3185,7 +3200,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ10">
         <v>0.75</v>
@@ -3519,7 +3534,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3725,7 +3740,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3806,7 +3821,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ13">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3931,7 +3946,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4137,7 +4152,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4549,7 +4564,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4833,7 +4848,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ18">
         <v>0.29</v>
@@ -5167,7 +5182,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5454,7 +5469,7 @@
         <v>2</v>
       </c>
       <c r="AQ21">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR21">
         <v>1.16</v>
@@ -5579,7 +5594,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -5657,7 +5672,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ22">
         <v>2.25</v>
@@ -5863,10 +5878,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ23">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR23">
         <v>1.5</v>
@@ -5991,7 +6006,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6072,7 +6087,7 @@
         <v>1</v>
       </c>
       <c r="AQ24">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR24">
         <v>1.03</v>
@@ -6197,7 +6212,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6403,7 +6418,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -6609,7 +6624,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q27">
         <v>2.63</v>
@@ -6815,7 +6830,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -6893,7 +6908,7 @@
         <v>1</v>
       </c>
       <c r="AP28">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ28">
         <v>2</v>
@@ -7021,7 +7036,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7227,7 +7242,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7305,7 +7320,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ30">
         <v>1</v>
@@ -7433,7 +7448,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7639,7 +7654,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7845,7 +7860,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -7926,7 +7941,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ33">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR33">
         <v>1.57</v>
@@ -8257,7 +8272,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -8338,7 +8353,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ35">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR35">
         <v>2.58</v>
@@ -8747,7 +8762,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ37">
         <v>1.63</v>
@@ -8875,7 +8890,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -8956,7 +8971,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ38">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR38">
         <v>1.73</v>
@@ -9162,7 +9177,7 @@
         <v>2</v>
       </c>
       <c r="AQ39">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR39">
         <v>1.56</v>
@@ -9287,7 +9302,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9365,7 +9380,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ40">
         <v>0.75</v>
@@ -9493,7 +9508,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9699,7 +9714,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -9777,7 +9792,7 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ42">
         <v>1.13</v>
@@ -10111,7 +10126,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10317,7 +10332,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10398,7 +10413,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ45">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR45">
         <v>1</v>
@@ -10523,7 +10538,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10601,7 +10616,7 @@
         <v>2</v>
       </c>
       <c r="AP46">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ46">
         <v>2</v>
@@ -10935,7 +10950,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11016,7 +11031,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ48">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR48">
         <v>2.42</v>
@@ -11347,7 +11362,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11553,7 +11568,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -11634,7 +11649,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ51">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR51">
         <v>1.37</v>
@@ -11759,7 +11774,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11837,7 +11852,7 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ52">
         <v>2</v>
@@ -12043,7 +12058,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ53">
         <v>1.63</v>
@@ -12171,7 +12186,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12377,7 +12392,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12583,7 +12598,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -12789,7 +12804,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -12870,7 +12885,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ57">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR57">
         <v>2.44</v>
@@ -13073,10 +13088,10 @@
         <v>0</v>
       </c>
       <c r="AP58">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ58">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR58">
         <v>1.68</v>
@@ -13201,7 +13216,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13279,7 +13294,7 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ59">
         <v>0.29</v>
@@ -13407,7 +13422,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13485,7 +13500,7 @@
         <v>2.33</v>
       </c>
       <c r="AP60">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ60">
         <v>1.63</v>
@@ -13613,7 +13628,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14025,7 +14040,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14106,7 +14121,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ63">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR63">
         <v>1.07</v>
@@ -14231,7 +14246,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14437,7 +14452,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14515,7 +14530,7 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ65">
         <v>1.14</v>
@@ -14643,7 +14658,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14927,10 +14942,10 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ67">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR67">
         <v>1.52</v>
@@ -15055,7 +15070,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15261,7 +15276,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q69">
         <v>1.8</v>
@@ -15342,7 +15357,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ69">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR69">
         <v>2.2</v>
@@ -15467,7 +15482,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15673,7 +15688,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -15879,7 +15894,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -15960,7 +15975,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ72">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR72">
         <v>1.22</v>
@@ -16163,7 +16178,7 @@
         <v>0.33</v>
       </c>
       <c r="AP73">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ73">
         <v>0.57</v>
@@ -16578,7 +16593,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ75">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR75">
         <v>1.82</v>
@@ -16703,7 +16718,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -16784,7 +16799,7 @@
         <v>2</v>
       </c>
       <c r="AQ76">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR76">
         <v>1.42</v>
@@ -16909,7 +16924,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -16987,7 +17002,7 @@
         <v>0.75</v>
       </c>
       <c r="AP77">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ77">
         <v>1.13</v>
@@ -17811,7 +17826,7 @@
         <v>2.33</v>
       </c>
       <c r="AP81">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ81">
         <v>2</v>
@@ -18351,7 +18366,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18429,7 +18444,7 @@
         <v>2.6</v>
       </c>
       <c r="AP84">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ84">
         <v>2.13</v>
@@ -18557,7 +18572,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q85">
         <v>2.1</v>
@@ -18638,7 +18653,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ85">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR85">
         <v>0.97</v>
@@ -18763,7 +18778,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -18841,7 +18856,7 @@
         <v>0.25</v>
       </c>
       <c r="AP86">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ86">
         <v>0.71</v>
@@ -18969,7 +18984,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19587,7 +19602,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19668,7 +19683,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ90">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR90">
         <v>2.13</v>
@@ -19793,7 +19808,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -19871,10 +19886,10 @@
         <v>1.75</v>
       </c>
       <c r="AP91">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ91">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR91">
         <v>1.38</v>
@@ -20205,7 +20220,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -20492,7 +20507,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ94">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR94">
         <v>2.18</v>
@@ -20823,7 +20838,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -20901,7 +20916,7 @@
         <v>2</v>
       </c>
       <c r="AP96">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ96">
         <v>1.63</v>
@@ -21110,7 +21125,7 @@
         <v>1</v>
       </c>
       <c r="AQ97">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR97">
         <v>1.25</v>
@@ -21441,7 +21456,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -21853,7 +21868,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -21931,10 +21946,10 @@
         <v>0.4</v>
       </c>
       <c r="AP101">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ101">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR101">
         <v>1.26</v>
@@ -22059,7 +22074,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22265,7 +22280,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22343,7 +22358,7 @@
         <v>1</v>
       </c>
       <c r="AP103">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ103">
         <v>1.14</v>
@@ -22552,7 +22567,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ104">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR104">
         <v>1.72</v>
@@ -22677,7 +22692,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -22758,7 +22773,7 @@
         <v>2</v>
       </c>
       <c r="AQ105">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR105">
         <v>1.47</v>
@@ -22883,7 +22898,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -23089,7 +23104,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23373,7 +23388,7 @@
         <v>0.6</v>
       </c>
       <c r="AP108">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ108">
         <v>0.57</v>
@@ -23501,7 +23516,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -23579,10 +23594,10 @@
         <v>1.67</v>
       </c>
       <c r="AP109">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ109">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR109">
         <v>1.42</v>
@@ -23707,7 +23722,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -23788,7 +23803,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ110">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR110">
         <v>2.1</v>
@@ -23913,7 +23928,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24119,7 +24134,7 @@
         <v>96</v>
       </c>
       <c r="P112" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q112">
         <v>3.4</v>
@@ -24325,7 +24340,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24531,7 +24546,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -24737,7 +24752,7 @@
         <v>169</v>
       </c>
       <c r="P115" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q115">
         <v>1.62</v>
@@ -24943,7 +24958,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25149,7 +25164,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25355,7 +25370,7 @@
         <v>171</v>
       </c>
       <c r="P118" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25433,7 +25448,7 @@
         <v>1.17</v>
       </c>
       <c r="AP118">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ118">
         <v>1</v>
@@ -25561,7 +25576,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -25639,10 +25654,10 @@
         <v>2.17</v>
       </c>
       <c r="AP119">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ119">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR119">
         <v>1.52</v>
@@ -25767,7 +25782,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -25848,7 +25863,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ120">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR120">
         <v>1.27</v>
@@ -25973,7 +25988,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26051,7 +26066,7 @@
         <v>2.43</v>
       </c>
       <c r="AP121">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ121">
         <v>2.13</v>
@@ -26179,7 +26194,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26385,7 +26400,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q123">
         <v>1.91</v>
@@ -26466,7 +26481,7 @@
         <v>2</v>
       </c>
       <c r="AQ123">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR123">
         <v>1.56</v>
@@ -26591,7 +26606,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26669,7 +26684,7 @@
         <v>1.86</v>
       </c>
       <c r="AP124">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ124">
         <v>2</v>
@@ -26797,7 +26812,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -26875,7 +26890,7 @@
         <v>1</v>
       </c>
       <c r="AP125">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ125">
         <v>1.29</v>
@@ -27003,7 +27018,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27209,7 +27224,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27290,7 +27305,7 @@
         <v>2</v>
       </c>
       <c r="AQ127">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR127">
         <v>1.42</v>
@@ -27415,7 +27430,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27621,7 +27636,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27827,7 +27842,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -28033,7 +28048,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28239,7 +28254,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28317,7 +28332,7 @@
         <v>0.83</v>
       </c>
       <c r="AP132">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ132">
         <v>1.14</v>
@@ -28445,7 +28460,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28526,7 +28541,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ133">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR133">
         <v>1.24</v>
@@ -29063,7 +29078,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29269,7 +29284,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -29426,6 +29441,1036 @@
       </c>
       <c r="BP137">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:68">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>7491951</v>
+      </c>
+      <c r="C138" t="s">
+        <v>68</v>
+      </c>
+      <c r="D138" t="s">
+        <v>69</v>
+      </c>
+      <c r="E138" s="2">
+        <v>45668.47916666666</v>
+      </c>
+      <c r="F138">
+        <v>16</v>
+      </c>
+      <c r="G138" t="s">
+        <v>72</v>
+      </c>
+      <c r="H138" t="s">
+        <v>77</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>1</v>
+      </c>
+      <c r="K138">
+        <v>1</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>1</v>
+      </c>
+      <c r="N138">
+        <v>1</v>
+      </c>
+      <c r="O138" t="s">
+        <v>96</v>
+      </c>
+      <c r="P138" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q138">
+        <v>2.88</v>
+      </c>
+      <c r="R138">
+        <v>2.38</v>
+      </c>
+      <c r="S138">
+        <v>3.25</v>
+      </c>
+      <c r="T138">
+        <v>1.29</v>
+      </c>
+      <c r="U138">
+        <v>3.5</v>
+      </c>
+      <c r="V138">
+        <v>2.38</v>
+      </c>
+      <c r="W138">
+        <v>1.53</v>
+      </c>
+      <c r="X138">
+        <v>5.5</v>
+      </c>
+      <c r="Y138">
+        <v>1.14</v>
+      </c>
+      <c r="Z138">
+        <v>2.3</v>
+      </c>
+      <c r="AA138">
+        <v>3.7</v>
+      </c>
+      <c r="AB138">
+        <v>2.8</v>
+      </c>
+      <c r="AC138">
+        <v>1.03</v>
+      </c>
+      <c r="AD138">
+        <v>15</v>
+      </c>
+      <c r="AE138">
+        <v>1.19</v>
+      </c>
+      <c r="AF138">
+        <v>4.75</v>
+      </c>
+      <c r="AG138">
+        <v>1.58</v>
+      </c>
+      <c r="AH138">
+        <v>2.25</v>
+      </c>
+      <c r="AI138">
+        <v>1.5</v>
+      </c>
+      <c r="AJ138">
+        <v>2.5</v>
+      </c>
+      <c r="AK138">
+        <v>1.41</v>
+      </c>
+      <c r="AL138">
+        <v>1.28</v>
+      </c>
+      <c r="AM138">
+        <v>1.57</v>
+      </c>
+      <c r="AN138">
+        <v>1.25</v>
+      </c>
+      <c r="AO138">
+        <v>1.86</v>
+      </c>
+      <c r="AP138">
+        <v>1.11</v>
+      </c>
+      <c r="AQ138">
+        <v>2</v>
+      </c>
+      <c r="AR138">
+        <v>1.83</v>
+      </c>
+      <c r="AS138">
+        <v>1.41</v>
+      </c>
+      <c r="AT138">
+        <v>3.24</v>
+      </c>
+      <c r="AU138">
+        <v>3</v>
+      </c>
+      <c r="AV138">
+        <v>4</v>
+      </c>
+      <c r="AW138">
+        <v>13</v>
+      </c>
+      <c r="AX138">
+        <v>9</v>
+      </c>
+      <c r="AY138">
+        <v>22</v>
+      </c>
+      <c r="AZ138">
+        <v>16</v>
+      </c>
+      <c r="BA138">
+        <v>4</v>
+      </c>
+      <c r="BB138">
+        <v>8</v>
+      </c>
+      <c r="BC138">
+        <v>12</v>
+      </c>
+      <c r="BD138">
+        <v>1.79</v>
+      </c>
+      <c r="BE138">
+        <v>6.5</v>
+      </c>
+      <c r="BF138">
+        <v>2.23</v>
+      </c>
+      <c r="BG138">
+        <v>1.27</v>
+      </c>
+      <c r="BH138">
+        <v>3.3</v>
+      </c>
+      <c r="BI138">
+        <v>1.48</v>
+      </c>
+      <c r="BJ138">
+        <v>2.45</v>
+      </c>
+      <c r="BK138">
+        <v>1.76</v>
+      </c>
+      <c r="BL138">
+        <v>1.93</v>
+      </c>
+      <c r="BM138">
+        <v>2.18</v>
+      </c>
+      <c r="BN138">
+        <v>1.58</v>
+      </c>
+      <c r="BO138">
+        <v>2.8</v>
+      </c>
+      <c r="BP138">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="139" spans="1:68">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>7491952</v>
+      </c>
+      <c r="C139" t="s">
+        <v>68</v>
+      </c>
+      <c r="D139" t="s">
+        <v>69</v>
+      </c>
+      <c r="E139" s="2">
+        <v>45668.47916666666</v>
+      </c>
+      <c r="F139">
+        <v>16</v>
+      </c>
+      <c r="G139" t="s">
+        <v>86</v>
+      </c>
+      <c r="H139" t="s">
+        <v>79</v>
+      </c>
+      <c r="I139">
+        <v>1</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>1</v>
+      </c>
+      <c r="L139">
+        <v>2</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="N139">
+        <v>2</v>
+      </c>
+      <c r="O139" t="s">
+        <v>187</v>
+      </c>
+      <c r="P139" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q139">
+        <v>3.75</v>
+      </c>
+      <c r="R139">
+        <v>2.1</v>
+      </c>
+      <c r="S139">
+        <v>3</v>
+      </c>
+      <c r="T139">
+        <v>1.44</v>
+      </c>
+      <c r="U139">
+        <v>2.63</v>
+      </c>
+      <c r="V139">
+        <v>3.25</v>
+      </c>
+      <c r="W139">
+        <v>1.33</v>
+      </c>
+      <c r="X139">
+        <v>9</v>
+      </c>
+      <c r="Y139">
+        <v>1.07</v>
+      </c>
+      <c r="Z139">
+        <v>2.75</v>
+      </c>
+      <c r="AA139">
+        <v>3.25</v>
+      </c>
+      <c r="AB139">
+        <v>2.55</v>
+      </c>
+      <c r="AC139">
+        <v>1.07</v>
+      </c>
+      <c r="AD139">
+        <v>10</v>
+      </c>
+      <c r="AE139">
+        <v>1.33</v>
+      </c>
+      <c r="AF139">
+        <v>3.3</v>
+      </c>
+      <c r="AG139">
+        <v>2</v>
+      </c>
+      <c r="AH139">
+        <v>1.71</v>
+      </c>
+      <c r="AI139">
+        <v>1.8</v>
+      </c>
+      <c r="AJ139">
+        <v>1.95</v>
+      </c>
+      <c r="AK139">
+        <v>1.58</v>
+      </c>
+      <c r="AL139">
+        <v>1.33</v>
+      </c>
+      <c r="AM139">
+        <v>1.35</v>
+      </c>
+      <c r="AN139">
+        <v>0.57</v>
+      </c>
+      <c r="AO139">
+        <v>0.63</v>
+      </c>
+      <c r="AP139">
+        <v>0.88</v>
+      </c>
+      <c r="AQ139">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR139">
+        <v>1.27</v>
+      </c>
+      <c r="AS139">
+        <v>1.18</v>
+      </c>
+      <c r="AT139">
+        <v>2.45</v>
+      </c>
+      <c r="AU139">
+        <v>10</v>
+      </c>
+      <c r="AV139">
+        <v>7</v>
+      </c>
+      <c r="AW139">
+        <v>7</v>
+      </c>
+      <c r="AX139">
+        <v>4</v>
+      </c>
+      <c r="AY139">
+        <v>19</v>
+      </c>
+      <c r="AZ139">
+        <v>12</v>
+      </c>
+      <c r="BA139">
+        <v>5</v>
+      </c>
+      <c r="BB139">
+        <v>4</v>
+      </c>
+      <c r="BC139">
+        <v>9</v>
+      </c>
+      <c r="BD139">
+        <v>2.12</v>
+      </c>
+      <c r="BE139">
+        <v>6.4</v>
+      </c>
+      <c r="BF139">
+        <v>1.86</v>
+      </c>
+      <c r="BG139">
+        <v>1.29</v>
+      </c>
+      <c r="BH139">
+        <v>3.15</v>
+      </c>
+      <c r="BI139">
+        <v>1.5</v>
+      </c>
+      <c r="BJ139">
+        <v>2.35</v>
+      </c>
+      <c r="BK139">
+        <v>1.84</v>
+      </c>
+      <c r="BL139">
+        <v>1.84</v>
+      </c>
+      <c r="BM139">
+        <v>2.3</v>
+      </c>
+      <c r="BN139">
+        <v>1.53</v>
+      </c>
+      <c r="BO139">
+        <v>3</v>
+      </c>
+      <c r="BP139">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="140" spans="1:68">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>7491953</v>
+      </c>
+      <c r="C140" t="s">
+        <v>68</v>
+      </c>
+      <c r="D140" t="s">
+        <v>69</v>
+      </c>
+      <c r="E140" s="2">
+        <v>45668.47916666666</v>
+      </c>
+      <c r="F140">
+        <v>16</v>
+      </c>
+      <c r="G140" t="s">
+        <v>73</v>
+      </c>
+      <c r="H140" t="s">
+        <v>81</v>
+      </c>
+      <c r="I140">
+        <v>2</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>2</v>
+      </c>
+      <c r="L140">
+        <v>3</v>
+      </c>
+      <c r="M140">
+        <v>2</v>
+      </c>
+      <c r="N140">
+        <v>5</v>
+      </c>
+      <c r="O140" t="s">
+        <v>188</v>
+      </c>
+      <c r="P140" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q140">
+        <v>1.83</v>
+      </c>
+      <c r="R140">
+        <v>2.6</v>
+      </c>
+      <c r="S140">
+        <v>6.5</v>
+      </c>
+      <c r="T140">
+        <v>1.29</v>
+      </c>
+      <c r="U140">
+        <v>3.5</v>
+      </c>
+      <c r="V140">
+        <v>2.25</v>
+      </c>
+      <c r="W140">
+        <v>1.57</v>
+      </c>
+      <c r="X140">
+        <v>5.5</v>
+      </c>
+      <c r="Y140">
+        <v>1.14</v>
+      </c>
+      <c r="Z140">
+        <v>1.36</v>
+      </c>
+      <c r="AA140">
+        <v>5</v>
+      </c>
+      <c r="AB140">
+        <v>8.25</v>
+      </c>
+      <c r="AC140">
+        <v>1.02</v>
+      </c>
+      <c r="AD140">
+        <v>19</v>
+      </c>
+      <c r="AE140">
+        <v>1.18</v>
+      </c>
+      <c r="AF140">
+        <v>5</v>
+      </c>
+      <c r="AG140">
+        <v>1.54</v>
+      </c>
+      <c r="AH140">
+        <v>2.38</v>
+      </c>
+      <c r="AI140">
+        <v>1.8</v>
+      </c>
+      <c r="AJ140">
+        <v>1.95</v>
+      </c>
+      <c r="AK140">
+        <v>1.09</v>
+      </c>
+      <c r="AL140">
+        <v>1.17</v>
+      </c>
+      <c r="AM140">
+        <v>2.95</v>
+      </c>
+      <c r="AN140">
+        <v>2.29</v>
+      </c>
+      <c r="AO140">
+        <v>0.29</v>
+      </c>
+      <c r="AP140">
+        <v>2.38</v>
+      </c>
+      <c r="AQ140">
+        <v>0.25</v>
+      </c>
+      <c r="AR140">
+        <v>1.59</v>
+      </c>
+      <c r="AS140">
+        <v>1.14</v>
+      </c>
+      <c r="AT140">
+        <v>2.73</v>
+      </c>
+      <c r="AU140">
+        <v>6</v>
+      </c>
+      <c r="AV140">
+        <v>8</v>
+      </c>
+      <c r="AW140">
+        <v>9</v>
+      </c>
+      <c r="AX140">
+        <v>7</v>
+      </c>
+      <c r="AY140">
+        <v>19</v>
+      </c>
+      <c r="AZ140">
+        <v>18</v>
+      </c>
+      <c r="BA140">
+        <v>7</v>
+      </c>
+      <c r="BB140">
+        <v>1</v>
+      </c>
+      <c r="BC140">
+        <v>8</v>
+      </c>
+      <c r="BD140">
+        <v>1.27</v>
+      </c>
+      <c r="BE140">
+        <v>8</v>
+      </c>
+      <c r="BF140">
+        <v>4.1</v>
+      </c>
+      <c r="BG140">
+        <v>1.23</v>
+      </c>
+      <c r="BH140">
+        <v>3.65</v>
+      </c>
+      <c r="BI140">
+        <v>1.41</v>
+      </c>
+      <c r="BJ140">
+        <v>2.65</v>
+      </c>
+      <c r="BK140">
+        <v>1.65</v>
+      </c>
+      <c r="BL140">
+        <v>2.07</v>
+      </c>
+      <c r="BM140">
+        <v>2.04</v>
+      </c>
+      <c r="BN140">
+        <v>1.68</v>
+      </c>
+      <c r="BO140">
+        <v>2.55</v>
+      </c>
+      <c r="BP140">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="141" spans="1:68">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>7491955</v>
+      </c>
+      <c r="C141" t="s">
+        <v>68</v>
+      </c>
+      <c r="D141" t="s">
+        <v>69</v>
+      </c>
+      <c r="E141" s="2">
+        <v>45668.47916666666</v>
+      </c>
+      <c r="F141">
+        <v>16</v>
+      </c>
+      <c r="G141" t="s">
+        <v>75</v>
+      </c>
+      <c r="H141" t="s">
+        <v>83</v>
+      </c>
+      <c r="I141">
+        <v>1</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <v>1</v>
+      </c>
+      <c r="L141">
+        <v>2</v>
+      </c>
+      <c r="M141">
+        <v>0</v>
+      </c>
+      <c r="N141">
+        <v>2</v>
+      </c>
+      <c r="O141" t="s">
+        <v>189</v>
+      </c>
+      <c r="P141" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q141">
+        <v>2.1</v>
+      </c>
+      <c r="R141">
+        <v>2.38</v>
+      </c>
+      <c r="S141">
+        <v>5.5</v>
+      </c>
+      <c r="T141">
+        <v>1.33</v>
+      </c>
+      <c r="U141">
+        <v>3.25</v>
+      </c>
+      <c r="V141">
+        <v>2.63</v>
+      </c>
+      <c r="W141">
+        <v>1.44</v>
+      </c>
+      <c r="X141">
+        <v>6.5</v>
+      </c>
+      <c r="Y141">
+        <v>1.11</v>
+      </c>
+      <c r="Z141">
+        <v>1.46</v>
+      </c>
+      <c r="AA141">
+        <v>4.75</v>
+      </c>
+      <c r="AB141">
+        <v>6.25</v>
+      </c>
+      <c r="AC141">
+        <v>1.03</v>
+      </c>
+      <c r="AD141">
+        <v>15</v>
+      </c>
+      <c r="AE141">
+        <v>1.22</v>
+      </c>
+      <c r="AF141">
+        <v>4.33</v>
+      </c>
+      <c r="AG141">
+        <v>1.55</v>
+      </c>
+      <c r="AH141">
+        <v>2.3</v>
+      </c>
+      <c r="AI141">
+        <v>1.8</v>
+      </c>
+      <c r="AJ141">
+        <v>1.95</v>
+      </c>
+      <c r="AK141">
+        <v>1.13</v>
+      </c>
+      <c r="AL141">
+        <v>1.21</v>
+      </c>
+      <c r="AM141">
+        <v>2.45</v>
+      </c>
+      <c r="AN141">
+        <v>1.38</v>
+      </c>
+      <c r="AO141">
+        <v>0.13</v>
+      </c>
+      <c r="AP141">
+        <v>1.56</v>
+      </c>
+      <c r="AQ141">
+        <v>0.11</v>
+      </c>
+      <c r="AR141">
+        <v>1.48</v>
+      </c>
+      <c r="AS141">
+        <v>1.17</v>
+      </c>
+      <c r="AT141">
+        <v>2.65</v>
+      </c>
+      <c r="AU141">
+        <v>6</v>
+      </c>
+      <c r="AV141">
+        <v>3</v>
+      </c>
+      <c r="AW141">
+        <v>5</v>
+      </c>
+      <c r="AX141">
+        <v>10</v>
+      </c>
+      <c r="AY141">
+        <v>12</v>
+      </c>
+      <c r="AZ141">
+        <v>17</v>
+      </c>
+      <c r="BA141">
+        <v>5</v>
+      </c>
+      <c r="BB141">
+        <v>6</v>
+      </c>
+      <c r="BC141">
+        <v>11</v>
+      </c>
+      <c r="BD141">
+        <v>1.33</v>
+      </c>
+      <c r="BE141">
+        <v>7.5</v>
+      </c>
+      <c r="BF141">
+        <v>3.65</v>
+      </c>
+      <c r="BG141">
+        <v>1.23</v>
+      </c>
+      <c r="BH141">
+        <v>3.65</v>
+      </c>
+      <c r="BI141">
+        <v>1.41</v>
+      </c>
+      <c r="BJ141">
+        <v>2.65</v>
+      </c>
+      <c r="BK141">
+        <v>1.66</v>
+      </c>
+      <c r="BL141">
+        <v>2.06</v>
+      </c>
+      <c r="BM141">
+        <v>2.04</v>
+      </c>
+      <c r="BN141">
+        <v>1.68</v>
+      </c>
+      <c r="BO141">
+        <v>2.55</v>
+      </c>
+      <c r="BP141">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="142" spans="1:68">
+      <c r="A142" s="1">
+        <v>141</v>
+      </c>
+      <c r="B142">
+        <v>7491957</v>
+      </c>
+      <c r="C142" t="s">
+        <v>68</v>
+      </c>
+      <c r="D142" t="s">
+        <v>69</v>
+      </c>
+      <c r="E142" s="2">
+        <v>45668.47916666666</v>
+      </c>
+      <c r="F142">
+        <v>16</v>
+      </c>
+      <c r="G142" t="s">
+        <v>78</v>
+      </c>
+      <c r="H142" t="s">
+        <v>82</v>
+      </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
+      <c r="J142">
+        <v>1</v>
+      </c>
+      <c r="K142">
+        <v>1</v>
+      </c>
+      <c r="L142">
+        <v>0</v>
+      </c>
+      <c r="M142">
+        <v>1</v>
+      </c>
+      <c r="N142">
+        <v>1</v>
+      </c>
+      <c r="O142" t="s">
+        <v>96</v>
+      </c>
+      <c r="P142" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q142">
+        <v>4</v>
+      </c>
+      <c r="R142">
+        <v>2.25</v>
+      </c>
+      <c r="S142">
+        <v>2.63</v>
+      </c>
+      <c r="T142">
+        <v>1.36</v>
+      </c>
+      <c r="U142">
+        <v>3</v>
+      </c>
+      <c r="V142">
+        <v>2.63</v>
+      </c>
+      <c r="W142">
+        <v>1.44</v>
+      </c>
+      <c r="X142">
+        <v>7</v>
+      </c>
+      <c r="Y142">
+        <v>1.1</v>
+      </c>
+      <c r="Z142">
+        <v>3.3</v>
+      </c>
+      <c r="AA142">
+        <v>3.6</v>
+      </c>
+      <c r="AB142">
+        <v>2.1</v>
+      </c>
+      <c r="AC142">
+        <v>1.04</v>
+      </c>
+      <c r="AD142">
+        <v>13</v>
+      </c>
+      <c r="AE142">
+        <v>1.26</v>
+      </c>
+      <c r="AF142">
+        <v>4</v>
+      </c>
+      <c r="AG142">
+        <v>1.71</v>
+      </c>
+      <c r="AH142">
+        <v>2</v>
+      </c>
+      <c r="AI142">
+        <v>1.67</v>
+      </c>
+      <c r="AJ142">
+        <v>2.1</v>
+      </c>
+      <c r="AK142">
+        <v>1.73</v>
+      </c>
+      <c r="AL142">
+        <v>1.28</v>
+      </c>
+      <c r="AM142">
+        <v>1.3</v>
+      </c>
+      <c r="AN142">
+        <v>0.71</v>
+      </c>
+      <c r="AO142">
+        <v>1.63</v>
+      </c>
+      <c r="AP142">
+        <v>0.63</v>
+      </c>
+      <c r="AQ142">
+        <v>1.78</v>
+      </c>
+      <c r="AR142">
+        <v>1.26</v>
+      </c>
+      <c r="AS142">
+        <v>1.39</v>
+      </c>
+      <c r="AT142">
+        <v>2.65</v>
+      </c>
+      <c r="AU142">
+        <v>5</v>
+      </c>
+      <c r="AV142">
+        <v>7</v>
+      </c>
+      <c r="AW142">
+        <v>14</v>
+      </c>
+      <c r="AX142">
+        <v>8</v>
+      </c>
+      <c r="AY142">
+        <v>21</v>
+      </c>
+      <c r="AZ142">
+        <v>17</v>
+      </c>
+      <c r="BA142">
+        <v>3</v>
+      </c>
+      <c r="BB142">
+        <v>3</v>
+      </c>
+      <c r="BC142">
+        <v>6</v>
+      </c>
+      <c r="BD142">
+        <v>2.2</v>
+      </c>
+      <c r="BE142">
+        <v>6.5</v>
+      </c>
+      <c r="BF142">
+        <v>1.8</v>
+      </c>
+      <c r="BG142">
+        <v>1.3</v>
+      </c>
+      <c r="BH142">
+        <v>3.1</v>
+      </c>
+      <c r="BI142">
+        <v>1.52</v>
+      </c>
+      <c r="BJ142">
+        <v>2.32</v>
+      </c>
+      <c r="BK142">
+        <v>1.86</v>
+      </c>
+      <c r="BL142">
+        <v>1.82</v>
+      </c>
+      <c r="BM142">
+        <v>2.33</v>
+      </c>
+      <c r="BN142">
+        <v>1.52</v>
+      </c>
+      <c r="BO142">
+        <v>3.05</v>
+      </c>
+      <c r="BP142">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="281">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1218,7 +1218,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP142"/>
+  <dimension ref="A1:BP143"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ2">
         <v>2.25</v>
@@ -2997,7 +2997,7 @@
         <v>1</v>
       </c>
       <c r="AQ9">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -6290,7 +6290,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ25">
         <v>1.29</v>
@@ -6499,7 +6499,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ26">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR26">
         <v>1.4</v>
@@ -7529,7 +7529,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ31">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR31">
         <v>0.65</v>
@@ -9174,7 +9174,7 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ39">
         <v>0.5600000000000001</v>
@@ -12267,7 +12267,7 @@
         <v>2</v>
       </c>
       <c r="AQ54">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR54">
         <v>1.7</v>
@@ -13706,7 +13706,7 @@
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ61">
         <v>0.75</v>
@@ -15769,7 +15769,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ71">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR71">
         <v>1.42</v>
@@ -18032,7 +18032,7 @@
         <v>2.5</v>
       </c>
       <c r="AP82">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ82">
         <v>2</v>
@@ -18447,7 +18447,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ84">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR84">
         <v>1.49</v>
@@ -21740,7 +21740,7 @@
         <v>1.2</v>
       </c>
       <c r="AP100">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ100">
         <v>1.13</v>
@@ -23185,7 +23185,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ107">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR107">
         <v>1.93</v>
@@ -25036,7 +25036,7 @@
         <v>0.2</v>
       </c>
       <c r="AP116">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ116">
         <v>0.71</v>
@@ -26069,7 +26069,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ121">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR121">
         <v>1.51</v>
@@ -26478,7 +26478,7 @@
         <v>0.33</v>
       </c>
       <c r="AP123">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ123">
         <v>0.25</v>
@@ -29589,16 +29589,16 @@
         <v>4</v>
       </c>
       <c r="AW138">
+        <v>4</v>
+      </c>
+      <c r="AX138">
+        <v>6</v>
+      </c>
+      <c r="AY138">
+        <v>16</v>
+      </c>
+      <c r="AZ138">
         <v>13</v>
-      </c>
-      <c r="AX138">
-        <v>9</v>
-      </c>
-      <c r="AY138">
-        <v>22</v>
-      </c>
-      <c r="AZ138">
-        <v>16</v>
       </c>
       <c r="BA138">
         <v>4</v>
@@ -29795,16 +29795,16 @@
         <v>7</v>
       </c>
       <c r="AW139">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX139">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY139">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ139">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA139">
         <v>5</v>
@@ -30207,16 +30207,16 @@
         <v>3</v>
       </c>
       <c r="AW141">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX141">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AY141">
+        <v>11</v>
+      </c>
+      <c r="AZ141">
         <v>12</v>
-      </c>
-      <c r="AZ141">
-        <v>17</v>
       </c>
       <c r="BA141">
         <v>5</v>
@@ -30413,16 +30413,16 @@
         <v>7</v>
       </c>
       <c r="AW142">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AX142">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY142">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AZ142">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA142">
         <v>3</v>
@@ -30471,6 +30471,212 @@
       </c>
       <c r="BP142">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="143" spans="1:68">
+      <c r="A143" s="1">
+        <v>142</v>
+      </c>
+      <c r="B143">
+        <v>7491956</v>
+      </c>
+      <c r="C143" t="s">
+        <v>68</v>
+      </c>
+      <c r="D143" t="s">
+        <v>69</v>
+      </c>
+      <c r="E143" s="2">
+        <v>45668.60416666666</v>
+      </c>
+      <c r="F143">
+        <v>16</v>
+      </c>
+      <c r="G143" t="s">
+        <v>70</v>
+      </c>
+      <c r="H143" t="s">
+        <v>87</v>
+      </c>
+      <c r="I143">
+        <v>0</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143">
+        <v>0</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143">
+        <v>1</v>
+      </c>
+      <c r="N143">
+        <v>1</v>
+      </c>
+      <c r="O143" t="s">
+        <v>96</v>
+      </c>
+      <c r="P143" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q143">
+        <v>5.5</v>
+      </c>
+      <c r="R143">
+        <v>2.75</v>
+      </c>
+      <c r="S143">
+        <v>1.83</v>
+      </c>
+      <c r="T143">
+        <v>1.2</v>
+      </c>
+      <c r="U143">
+        <v>4.33</v>
+      </c>
+      <c r="V143">
+        <v>1.91</v>
+      </c>
+      <c r="W143">
+        <v>1.8</v>
+      </c>
+      <c r="X143">
+        <v>4</v>
+      </c>
+      <c r="Y143">
+        <v>1.22</v>
+      </c>
+      <c r="Z143">
+        <v>6.5</v>
+      </c>
+      <c r="AA143">
+        <v>5</v>
+      </c>
+      <c r="AB143">
+        <v>1.33</v>
+      </c>
+      <c r="AC143">
+        <v>0</v>
+      </c>
+      <c r="AD143">
+        <v>0</v>
+      </c>
+      <c r="AE143">
+        <v>1.1</v>
+      </c>
+      <c r="AF143">
+        <v>7</v>
+      </c>
+      <c r="AG143">
+        <v>1.33</v>
+      </c>
+      <c r="AH143">
+        <v>3.2</v>
+      </c>
+      <c r="AI143">
+        <v>1.5</v>
+      </c>
+      <c r="AJ143">
+        <v>2.5</v>
+      </c>
+      <c r="AK143">
+        <v>2.8</v>
+      </c>
+      <c r="AL143">
+        <v>1.16</v>
+      </c>
+      <c r="AM143">
+        <v>1.12</v>
+      </c>
+      <c r="AN143">
+        <v>2</v>
+      </c>
+      <c r="AO143">
+        <v>2.13</v>
+      </c>
+      <c r="AP143">
+        <v>1.78</v>
+      </c>
+      <c r="AQ143">
+        <v>2.22</v>
+      </c>
+      <c r="AR143">
+        <v>1.59</v>
+      </c>
+      <c r="AS143">
+        <v>1.96</v>
+      </c>
+      <c r="AT143">
+        <v>3.55</v>
+      </c>
+      <c r="AU143">
+        <v>0</v>
+      </c>
+      <c r="AV143">
+        <v>11</v>
+      </c>
+      <c r="AW143">
+        <v>6</v>
+      </c>
+      <c r="AX143">
+        <v>13</v>
+      </c>
+      <c r="AY143">
+        <v>7</v>
+      </c>
+      <c r="AZ143">
+        <v>33</v>
+      </c>
+      <c r="BA143">
+        <v>4</v>
+      </c>
+      <c r="BB143">
+        <v>10</v>
+      </c>
+      <c r="BC143">
+        <v>14</v>
+      </c>
+      <c r="BD143">
+        <v>4.35</v>
+      </c>
+      <c r="BE143">
+        <v>7.5</v>
+      </c>
+      <c r="BF143">
+        <v>1.25</v>
+      </c>
+      <c r="BG143">
+        <v>1.33</v>
+      </c>
+      <c r="BH143">
+        <v>2.95</v>
+      </c>
+      <c r="BI143">
+        <v>1.56</v>
+      </c>
+      <c r="BJ143">
+        <v>2.23</v>
+      </c>
+      <c r="BK143">
+        <v>1.92</v>
+      </c>
+      <c r="BL143">
+        <v>1.77</v>
+      </c>
+      <c r="BM143">
+        <v>2.43</v>
+      </c>
+      <c r="BN143">
+        <v>1.48</v>
+      </c>
+      <c r="BO143">
+        <v>3.15</v>
+      </c>
+      <c r="BP143">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="283">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -586,6 +586,9 @@
     <t>['23', '69']</t>
   </si>
   <si>
+    <t>['23', '35', '47', '90']</t>
+  </si>
+  <si>
     <t>['12', '38', '90+11']</t>
   </si>
   <si>
@@ -857,6 +860,9 @@
   </si>
   <si>
     <t>['32']</t>
+  </si>
+  <si>
+    <t>['26', '90+3']</t>
   </si>
 </sst>
 </file>
@@ -1218,7 +1224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP143"/>
+  <dimension ref="A1:BP145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1474,7 +1480,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -1758,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ3">
         <v>0.11</v>
@@ -1886,7 +1892,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2092,7 +2098,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2173,7 +2179,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ5">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2298,7 +2304,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2376,10 +2382,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ6">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2504,7 +2510,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2916,7 +2922,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3122,7 +3128,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3534,7 +3540,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3740,7 +3746,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3946,7 +3952,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4152,7 +4158,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4564,7 +4570,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -5182,7 +5188,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5466,7 +5472,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ21">
         <v>0.5600000000000001</v>
@@ -5594,7 +5600,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -6006,7 +6012,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6212,7 +6218,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6293,7 +6299,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ25">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR25">
         <v>1.46</v>
@@ -6418,7 +6424,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -6624,7 +6630,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q27">
         <v>2.63</v>
@@ -6702,7 +6708,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ27">
         <v>1.13</v>
@@ -6830,7 +6836,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -6911,7 +6917,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ28">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR28">
         <v>1.23</v>
@@ -7036,7 +7042,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7114,7 +7120,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ29">
         <v>2</v>
@@ -7242,7 +7248,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7448,7 +7454,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7654,7 +7660,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7860,7 +7866,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8272,7 +8278,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -8890,7 +8896,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9302,7 +9308,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9508,7 +9514,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9589,7 +9595,7 @@
         <v>1</v>
       </c>
       <c r="AQ41">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR41">
         <v>1.28</v>
@@ -9714,7 +9720,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -9998,7 +10004,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ43">
         <v>0.29</v>
@@ -10126,7 +10132,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10332,7 +10338,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10538,7 +10544,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10619,7 +10625,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ46">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR46">
         <v>1.82</v>
@@ -10822,7 +10828,7 @@
         <v>1.5</v>
       </c>
       <c r="AP47">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ47">
         <v>1.14</v>
@@ -10950,7 +10956,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11362,7 +11368,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11568,7 +11574,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -11774,7 +11780,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12186,7 +12192,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12392,7 +12398,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12598,7 +12604,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -12804,7 +12810,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -13216,7 +13222,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13422,7 +13428,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13628,7 +13634,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -13915,7 +13921,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ62">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR62">
         <v>1.47</v>
@@ -14040,7 +14046,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14246,7 +14252,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14327,7 +14333,7 @@
         <v>1</v>
       </c>
       <c r="AQ64">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR64">
         <v>1.11</v>
@@ -14452,7 +14458,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14658,7 +14664,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14736,7 +14742,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ66">
         <v>0.71</v>
@@ -15070,7 +15076,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15148,7 +15154,7 @@
         <v>2</v>
       </c>
       <c r="AP68">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ68">
         <v>1</v>
@@ -15276,7 +15282,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q69">
         <v>1.8</v>
@@ -15482,7 +15488,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15688,7 +15694,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -15894,7 +15900,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16387,7 +16393,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ74">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR74">
         <v>2.41</v>
@@ -16718,7 +16724,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -16924,7 +16930,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -18035,7 +18041,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ82">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR82">
         <v>1.57</v>
@@ -18366,7 +18372,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18572,7 +18578,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q85">
         <v>2.1</v>
@@ -18778,7 +18784,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -18984,7 +18990,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19268,7 +19274,7 @@
         <v>1</v>
       </c>
       <c r="AP88">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ88">
         <v>1.14</v>
@@ -19474,7 +19480,7 @@
         <v>0.5</v>
       </c>
       <c r="AP89">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ89">
         <v>0.57</v>
@@ -19602,7 +19608,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19808,7 +19814,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -20220,7 +20226,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -20838,7 +20844,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21331,7 +21337,7 @@
         <v>2</v>
       </c>
       <c r="AQ98">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR98">
         <v>1.59</v>
@@ -21456,7 +21462,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -21868,7 +21874,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22074,7 +22080,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22280,7 +22286,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22564,7 +22570,7 @@
         <v>0</v>
       </c>
       <c r="AP104">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ104">
         <v>0.11</v>
@@ -22692,7 +22698,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -22770,7 +22776,7 @@
         <v>2</v>
       </c>
       <c r="AP105">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ105">
         <v>2</v>
@@ -22898,7 +22904,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -22979,7 +22985,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ106">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR106">
         <v>1.1</v>
@@ -23104,7 +23110,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23516,7 +23522,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -23722,7 +23728,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -23928,7 +23934,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24134,7 +24140,7 @@
         <v>96</v>
       </c>
       <c r="P112" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q112">
         <v>3.4</v>
@@ -24215,7 +24221,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ112">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR112">
         <v>1.23</v>
@@ -24340,7 +24346,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24546,7 +24552,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -24752,7 +24758,7 @@
         <v>169</v>
       </c>
       <c r="P115" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q115">
         <v>1.62</v>
@@ -24958,7 +24964,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25164,7 +25170,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25370,7 +25376,7 @@
         <v>171</v>
       </c>
       <c r="P118" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25576,7 +25582,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -25782,7 +25788,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -25988,7 +25994,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26194,7 +26200,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26272,7 +26278,7 @@
         <v>2</v>
       </c>
       <c r="AP122">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ122">
         <v>2.25</v>
@@ -26400,7 +26406,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q123">
         <v>1.91</v>
@@ -26606,7 +26612,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26687,7 +26693,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ124">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR124">
         <v>1.24</v>
@@ -26812,7 +26818,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -26893,7 +26899,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ125">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR125">
         <v>1.33</v>
@@ -27018,7 +27024,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27224,7 +27230,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27302,7 +27308,7 @@
         <v>1.86</v>
       </c>
       <c r="AP127">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ127">
         <v>1.78</v>
@@ -27430,7 +27436,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27636,7 +27642,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27842,7 +27848,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -28048,7 +28054,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28254,7 +28260,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28460,7 +28466,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -29078,7 +29084,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29284,7 +29290,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -29383,13 +29389,13 @@
         <v>6</v>
       </c>
       <c r="AW137">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AX137">
         <v>2</v>
       </c>
       <c r="AY137">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ137">
         <v>8</v>
@@ -29902,7 +29908,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q140">
         <v>1.83</v>
@@ -30001,16 +30007,16 @@
         <v>8</v>
       </c>
       <c r="AW140">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AX140">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AY140">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ140">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA140">
         <v>7</v>
@@ -30314,7 +30320,7 @@
         <v>96</v>
       </c>
       <c r="P142" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30520,7 +30526,7 @@
         <v>96</v>
       </c>
       <c r="P143" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -30619,16 +30625,16 @@
         <v>11</v>
       </c>
       <c r="AW143">
+        <v>4</v>
+      </c>
+      <c r="AX143">
+        <v>5</v>
+      </c>
+      <c r="AY143">
         <v>6</v>
       </c>
-      <c r="AX143">
-        <v>13</v>
-      </c>
-      <c r="AY143">
-        <v>7</v>
-      </c>
       <c r="AZ143">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="BA143">
         <v>4</v>
@@ -30677,6 +30683,418 @@
       </c>
       <c r="BP143">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="144" spans="1:68">
+      <c r="A144" s="1">
+        <v>143</v>
+      </c>
+      <c r="B144">
+        <v>7491949</v>
+      </c>
+      <c r="C144" t="s">
+        <v>68</v>
+      </c>
+      <c r="D144" t="s">
+        <v>69</v>
+      </c>
+      <c r="E144" s="2">
+        <v>45669.47916666666</v>
+      </c>
+      <c r="F144">
+        <v>16</v>
+      </c>
+      <c r="G144" t="s">
+        <v>71</v>
+      </c>
+      <c r="H144" t="s">
+        <v>84</v>
+      </c>
+      <c r="I144">
+        <v>2</v>
+      </c>
+      <c r="J144">
+        <v>1</v>
+      </c>
+      <c r="K144">
+        <v>3</v>
+      </c>
+      <c r="L144">
+        <v>4</v>
+      </c>
+      <c r="M144">
+        <v>2</v>
+      </c>
+      <c r="N144">
+        <v>6</v>
+      </c>
+      <c r="O144" t="s">
+        <v>190</v>
+      </c>
+      <c r="P144" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q144">
+        <v>2.25</v>
+      </c>
+      <c r="R144">
+        <v>2.5</v>
+      </c>
+      <c r="S144">
+        <v>4.33</v>
+      </c>
+      <c r="T144">
+        <v>1.25</v>
+      </c>
+      <c r="U144">
+        <v>3.75</v>
+      </c>
+      <c r="V144">
+        <v>2.25</v>
+      </c>
+      <c r="W144">
+        <v>1.57</v>
+      </c>
+      <c r="X144">
+        <v>5.5</v>
+      </c>
+      <c r="Y144">
+        <v>1.14</v>
+      </c>
+      <c r="Z144">
+        <v>1.62</v>
+      </c>
+      <c r="AA144">
+        <v>4.2</v>
+      </c>
+      <c r="AB144">
+        <v>4.5</v>
+      </c>
+      <c r="AC144">
+        <v>1.02</v>
+      </c>
+      <c r="AD144">
+        <v>21</v>
+      </c>
+      <c r="AE144">
+        <v>1.16</v>
+      </c>
+      <c r="AF144">
+        <v>5.5</v>
+      </c>
+      <c r="AG144">
+        <v>1.5</v>
+      </c>
+      <c r="AH144">
+        <v>2.55</v>
+      </c>
+      <c r="AI144">
+        <v>1.53</v>
+      </c>
+      <c r="AJ144">
+        <v>2.38</v>
+      </c>
+      <c r="AK144">
+        <v>1.22</v>
+      </c>
+      <c r="AL144">
+        <v>1.2</v>
+      </c>
+      <c r="AM144">
+        <v>2.15</v>
+      </c>
+      <c r="AN144">
+        <v>2</v>
+      </c>
+      <c r="AO144">
+        <v>2</v>
+      </c>
+      <c r="AP144">
+        <v>2.13</v>
+      </c>
+      <c r="AQ144">
+        <v>1.78</v>
+      </c>
+      <c r="AR144">
+        <v>1.49</v>
+      </c>
+      <c r="AS144">
+        <v>1.25</v>
+      </c>
+      <c r="AT144">
+        <v>2.74</v>
+      </c>
+      <c r="AU144">
+        <v>8</v>
+      </c>
+      <c r="AV144">
+        <v>3</v>
+      </c>
+      <c r="AW144">
+        <v>6</v>
+      </c>
+      <c r="AX144">
+        <v>1</v>
+      </c>
+      <c r="AY144">
+        <v>19</v>
+      </c>
+      <c r="AZ144">
+        <v>8</v>
+      </c>
+      <c r="BA144">
+        <v>4</v>
+      </c>
+      <c r="BB144">
+        <v>1</v>
+      </c>
+      <c r="BC144">
+        <v>5</v>
+      </c>
+      <c r="BD144">
+        <v>1.45</v>
+      </c>
+      <c r="BE144">
+        <v>6.75</v>
+      </c>
+      <c r="BF144">
+        <v>3.15</v>
+      </c>
+      <c r="BG144">
+        <v>1.29</v>
+      </c>
+      <c r="BH144">
+        <v>3.15</v>
+      </c>
+      <c r="BI144">
+        <v>1.49</v>
+      </c>
+      <c r="BJ144">
+        <v>2.4</v>
+      </c>
+      <c r="BK144">
+        <v>1.79</v>
+      </c>
+      <c r="BL144">
+        <v>1.9</v>
+      </c>
+      <c r="BM144">
+        <v>2.25</v>
+      </c>
+      <c r="BN144">
+        <v>1.55</v>
+      </c>
+      <c r="BO144">
+        <v>2.9</v>
+      </c>
+      <c r="BP144">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="145" spans="1:68">
+      <c r="A145" s="1">
+        <v>144</v>
+      </c>
+      <c r="B145">
+        <v>7491954</v>
+      </c>
+      <c r="C145" t="s">
+        <v>68</v>
+      </c>
+      <c r="D145" t="s">
+        <v>69</v>
+      </c>
+      <c r="E145" s="2">
+        <v>45669.5625</v>
+      </c>
+      <c r="F145">
+        <v>16</v>
+      </c>
+      <c r="G145" t="s">
+        <v>74</v>
+      </c>
+      <c r="H145" t="s">
+        <v>80</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+      <c r="J145">
+        <v>0</v>
+      </c>
+      <c r="K145">
+        <v>0</v>
+      </c>
+      <c r="L145">
+        <v>0</v>
+      </c>
+      <c r="M145">
+        <v>1</v>
+      </c>
+      <c r="N145">
+        <v>1</v>
+      </c>
+      <c r="O145" t="s">
+        <v>96</v>
+      </c>
+      <c r="P145" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q145">
+        <v>4</v>
+      </c>
+      <c r="R145">
+        <v>2.3</v>
+      </c>
+      <c r="S145">
+        <v>2.6</v>
+      </c>
+      <c r="T145">
+        <v>1.33</v>
+      </c>
+      <c r="U145">
+        <v>3.25</v>
+      </c>
+      <c r="V145">
+        <v>2.63</v>
+      </c>
+      <c r="W145">
+        <v>1.44</v>
+      </c>
+      <c r="X145">
+        <v>6.5</v>
+      </c>
+      <c r="Y145">
+        <v>1.11</v>
+      </c>
+      <c r="Z145">
+        <v>3.2</v>
+      </c>
+      <c r="AA145">
+        <v>3.6</v>
+      </c>
+      <c r="AB145">
+        <v>2.1</v>
+      </c>
+      <c r="AC145">
+        <v>1.04</v>
+      </c>
+      <c r="AD145">
+        <v>13</v>
+      </c>
+      <c r="AE145">
+        <v>1.24</v>
+      </c>
+      <c r="AF145">
+        <v>4.2</v>
+      </c>
+      <c r="AG145">
+        <v>1.61</v>
+      </c>
+      <c r="AH145">
+        <v>2.2</v>
+      </c>
+      <c r="AI145">
+        <v>1.62</v>
+      </c>
+      <c r="AJ145">
+        <v>2.2</v>
+      </c>
+      <c r="AK145">
+        <v>1.77</v>
+      </c>
+      <c r="AL145">
+        <v>1.27</v>
+      </c>
+      <c r="AM145">
+        <v>1.29</v>
+      </c>
+      <c r="AN145">
+        <v>1.75</v>
+      </c>
+      <c r="AO145">
+        <v>1.29</v>
+      </c>
+      <c r="AP145">
+        <v>1.56</v>
+      </c>
+      <c r="AQ145">
+        <v>1.5</v>
+      </c>
+      <c r="AR145">
+        <v>1.62</v>
+      </c>
+      <c r="AS145">
+        <v>1.15</v>
+      </c>
+      <c r="AT145">
+        <v>2.77</v>
+      </c>
+      <c r="AU145">
+        <v>3</v>
+      </c>
+      <c r="AV145">
+        <v>6</v>
+      </c>
+      <c r="AW145">
+        <v>6</v>
+      </c>
+      <c r="AX145">
+        <v>8</v>
+      </c>
+      <c r="AY145">
+        <v>9</v>
+      </c>
+      <c r="AZ145">
+        <v>17</v>
+      </c>
+      <c r="BA145">
+        <v>3</v>
+      </c>
+      <c r="BB145">
+        <v>9</v>
+      </c>
+      <c r="BC145">
+        <v>12</v>
+      </c>
+      <c r="BD145">
+        <v>2.43</v>
+      </c>
+      <c r="BE145">
+        <v>6.4</v>
+      </c>
+      <c r="BF145">
+        <v>1.68</v>
+      </c>
+      <c r="BG145">
+        <v>1.28</v>
+      </c>
+      <c r="BH145">
+        <v>3.2</v>
+      </c>
+      <c r="BI145">
+        <v>1.49</v>
+      </c>
+      <c r="BJ145">
+        <v>2.4</v>
+      </c>
+      <c r="BK145">
+        <v>1.8</v>
+      </c>
+      <c r="BL145">
+        <v>1.89</v>
+      </c>
+      <c r="BM145">
+        <v>2.25</v>
+      </c>
+      <c r="BN145">
+        <v>1.55</v>
+      </c>
+      <c r="BO145">
+        <v>2.9</v>
+      </c>
+      <c r="BP145">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="287">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -589,6 +589,18 @@
     <t>['23', '35', '47', '90']</t>
   </si>
   <si>
+    <t>['27', '32', '45+4', '90+8']</t>
+  </si>
+  <si>
+    <t>['43', '65', '71', '81']</t>
+  </si>
+  <si>
+    <t>['3', '60', '75', '83', '87']</t>
+  </si>
+  <si>
+    <t>['48']</t>
+  </si>
+  <si>
     <t>['12', '38', '90+11']</t>
   </si>
   <si>
@@ -751,9 +763,6 @@
     <t>['22']</t>
   </si>
   <si>
-    <t>['48']</t>
-  </si>
-  <si>
     <t>['40']</t>
   </si>
   <si>
@@ -863,6 +872,9 @@
   </si>
   <si>
     <t>['26', '90+3']</t>
+  </si>
+  <si>
+    <t>['71', '77']</t>
   </si>
 </sst>
 </file>
@@ -1224,7 +1236,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP145"/>
+  <dimension ref="A1:BP149"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1480,7 +1492,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -1892,7 +1904,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2098,7 +2110,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2304,7 +2316,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2510,7 +2522,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2922,7 +2934,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3000,7 +3012,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ9">
         <v>2.22</v>
@@ -3128,7 +3140,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3540,7 +3552,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3621,7 +3633,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ12">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3746,7 +3758,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3824,7 +3836,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ13">
         <v>2</v>
@@ -3952,7 +3964,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4030,7 +4042,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ14">
         <v>0.57</v>
@@ -4158,7 +4170,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4239,7 +4251,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ15">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4445,7 +4457,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ16">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4570,7 +4582,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4648,7 +4660,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ17">
         <v>1.63</v>
@@ -5063,7 +5075,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ19">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5188,7 +5200,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5600,7 +5612,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -6012,7 +6024,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6090,7 +6102,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ24">
         <v>1.78</v>
@@ -6218,7 +6230,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6424,7 +6436,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -6502,7 +6514,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ26">
         <v>2.22</v>
@@ -6630,7 +6642,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q27">
         <v>2.63</v>
@@ -6836,7 +6848,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7042,7 +7054,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7123,7 +7135,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ29">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR29">
         <v>1.7</v>
@@ -7248,7 +7260,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7329,7 +7341,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ30">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR30">
         <v>1.69</v>
@@ -7454,7 +7466,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7660,7 +7672,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7866,7 +7878,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8150,10 +8162,10 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ34">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR34">
         <v>1.86</v>
@@ -8278,7 +8290,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -8356,7 +8368,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ35">
         <v>2</v>
@@ -8565,7 +8577,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ36">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR36">
         <v>2.62</v>
@@ -8896,7 +8908,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9308,7 +9320,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9514,7 +9526,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9592,7 +9604,7 @@
         <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ41">
         <v>1.5</v>
@@ -9720,7 +9732,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -10132,7 +10144,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10338,7 +10350,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10416,7 +10428,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ45">
         <v>1.78</v>
@@ -10544,7 +10556,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10831,7 +10843,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ47">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR47">
         <v>2.02</v>
@@ -10956,7 +10968,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11034,7 +11046,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ48">
         <v>0.25</v>
@@ -11243,7 +11255,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ49">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR49">
         <v>0.41</v>
@@ -11368,7 +11380,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11449,7 +11461,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ50">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR50">
         <v>1.16</v>
@@ -11574,7 +11586,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -11780,7 +11792,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11861,7 +11873,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ52">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR52">
         <v>1.52</v>
@@ -12192,7 +12204,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12270,7 +12282,7 @@
         <v>3</v>
       </c>
       <c r="AP54">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ54">
         <v>2.22</v>
@@ -12398,7 +12410,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12604,7 +12616,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -12810,7 +12822,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -12888,7 +12900,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ57">
         <v>1.78</v>
@@ -13222,7 +13234,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13428,7 +13440,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13634,7 +13646,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14046,7 +14058,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14124,7 +14136,7 @@
         <v>0.67</v>
       </c>
       <c r="AP63">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ63">
         <v>0.5600000000000001</v>
@@ -14252,7 +14264,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14330,7 +14342,7 @@
         <v>2.33</v>
       </c>
       <c r="AP64">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ64">
         <v>1.78</v>
@@ -14458,7 +14470,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14539,7 +14551,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ65">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR65">
         <v>1.22</v>
@@ -14664,7 +14676,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14745,7 +14757,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ66">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR66">
         <v>1.91</v>
@@ -15076,7 +15088,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15157,7 +15169,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ68">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR68">
         <v>1.33</v>
@@ -15282,7 +15294,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q69">
         <v>1.8</v>
@@ -15488,7 +15500,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15694,7 +15706,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -15900,7 +15912,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16390,7 +16402,7 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ74">
         <v>1.5</v>
@@ -16724,7 +16736,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -16802,7 +16814,7 @@
         <v>0</v>
       </c>
       <c r="AP76">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ76">
         <v>0.11</v>
@@ -16930,7 +16942,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -17214,7 +17226,7 @@
         <v>1.5</v>
       </c>
       <c r="AP78">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ78">
         <v>0.75</v>
@@ -17420,7 +17432,7 @@
         <v>0</v>
       </c>
       <c r="AP79">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ79">
         <v>0.29</v>
@@ -17835,7 +17847,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ81">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR81">
         <v>1.64</v>
@@ -18247,7 +18259,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ83">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR83">
         <v>1.3</v>
@@ -18372,7 +18384,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18578,7 +18590,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>245</v>
+        <v>194</v>
       </c>
       <c r="Q85">
         <v>2.1</v>
@@ -18784,7 +18796,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -18865,7 +18877,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ86">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR86">
         <v>1.34</v>
@@ -18990,7 +19002,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19277,7 +19289,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ88">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR88">
         <v>1.44</v>
@@ -19608,7 +19620,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19814,7 +19826,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -20226,7 +20238,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -20304,7 +20316,7 @@
         <v>1.2</v>
       </c>
       <c r="AP93">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ93">
         <v>0.75</v>
@@ -20719,7 +20731,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ95">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR95">
         <v>1.86</v>
@@ -20844,7 +20856,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21128,7 +21140,7 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ97">
         <v>0.5600000000000001</v>
@@ -21334,7 +21346,7 @@
         <v>2</v>
       </c>
       <c r="AP98">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ98">
         <v>1.78</v>
@@ -21462,7 +21474,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -21540,10 +21552,10 @@
         <v>2</v>
       </c>
       <c r="AP99">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ99">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR99">
         <v>1.21</v>
@@ -21874,7 +21886,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22080,7 +22092,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22286,7 +22298,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22367,7 +22379,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ103">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR103">
         <v>1.49</v>
@@ -22698,7 +22710,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -22904,7 +22916,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -23110,7 +23122,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23522,7 +23534,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -23728,7 +23740,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -23934,7 +23946,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24012,7 +24024,7 @@
         <v>1.67</v>
       </c>
       <c r="AP111">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ111">
         <v>1.63</v>
@@ -24140,7 +24152,7 @@
         <v>96</v>
       </c>
       <c r="P112" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q112">
         <v>3.4</v>
@@ -24346,7 +24358,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24424,7 +24436,7 @@
         <v>0.2</v>
       </c>
       <c r="AP113">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ113">
         <v>0.29</v>
@@ -24552,7 +24564,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -24758,7 +24770,7 @@
         <v>169</v>
       </c>
       <c r="P115" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q115">
         <v>1.62</v>
@@ -24836,7 +24848,7 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ115">
         <v>1.13</v>
@@ -24964,7 +24976,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25045,7 +25057,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ116">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR116">
         <v>1.64</v>
@@ -25170,7 +25182,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25248,10 +25260,10 @@
         <v>2.2</v>
       </c>
       <c r="AP117">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ117">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR117">
         <v>1.29</v>
@@ -25376,7 +25388,7 @@
         <v>171</v>
       </c>
       <c r="P118" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25457,7 +25469,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ118">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR118">
         <v>1.77</v>
@@ -25582,7 +25594,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -25788,7 +25800,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -25994,7 +26006,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26200,7 +26212,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26406,7 +26418,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q123">
         <v>1.91</v>
@@ -26612,7 +26624,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26818,7 +26830,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -27024,7 +27036,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27230,7 +27242,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27436,7 +27448,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27642,7 +27654,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27720,7 +27732,7 @@
         <v>0.33</v>
       </c>
       <c r="AP129">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ129">
         <v>0.29</v>
@@ -27848,7 +27860,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -28054,7 +28066,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28132,10 +28144,10 @@
         <v>1.83</v>
       </c>
       <c r="AP131">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ131">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR131">
         <v>1.54</v>
@@ -28260,7 +28272,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28341,7 +28353,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ132">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR132">
         <v>1.76</v>
@@ -28466,7 +28478,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28750,10 +28762,10 @@
         <v>1.14</v>
       </c>
       <c r="AP134">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ134">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR134">
         <v>2.13</v>
@@ -29084,7 +29096,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29162,10 +29174,10 @@
         <v>0.33</v>
       </c>
       <c r="AP136">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ136">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR136">
         <v>1.28</v>
@@ -29290,7 +29302,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -29908,7 +29920,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q140">
         <v>1.83</v>
@@ -30320,7 +30332,7 @@
         <v>96</v>
       </c>
       <c r="P142" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30526,7 +30538,7 @@
         <v>96</v>
       </c>
       <c r="P143" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -30732,7 +30744,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -30938,7 +30950,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31095,6 +31107,830 @@
       </c>
       <c r="BP145">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="146" spans="1:68">
+      <c r="A146" s="1">
+        <v>145</v>
+      </c>
+      <c r="B146">
+        <v>7491966</v>
+      </c>
+      <c r="C146" t="s">
+        <v>68</v>
+      </c>
+      <c r="D146" t="s">
+        <v>69</v>
+      </c>
+      <c r="E146" s="2">
+        <v>45671.60416666666</v>
+      </c>
+      <c r="F146">
+        <v>17</v>
+      </c>
+      <c r="G146" t="s">
+        <v>81</v>
+      </c>
+      <c r="H146" t="s">
+        <v>76</v>
+      </c>
+      <c r="I146">
+        <v>3</v>
+      </c>
+      <c r="J146">
+        <v>0</v>
+      </c>
+      <c r="K146">
+        <v>3</v>
+      </c>
+      <c r="L146">
+        <v>4</v>
+      </c>
+      <c r="M146">
+        <v>2</v>
+      </c>
+      <c r="N146">
+        <v>6</v>
+      </c>
+      <c r="O146" t="s">
+        <v>191</v>
+      </c>
+      <c r="P146" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q146">
+        <v>5.5</v>
+      </c>
+      <c r="R146">
+        <v>2.63</v>
+      </c>
+      <c r="S146">
+        <v>1.91</v>
+      </c>
+      <c r="T146">
+        <v>1.22</v>
+      </c>
+      <c r="U146">
+        <v>4</v>
+      </c>
+      <c r="V146">
+        <v>2.1</v>
+      </c>
+      <c r="W146">
+        <v>1.67</v>
+      </c>
+      <c r="X146">
+        <v>4.5</v>
+      </c>
+      <c r="Y146">
+        <v>1.18</v>
+      </c>
+      <c r="Z146">
+        <v>6</v>
+      </c>
+      <c r="AA146">
+        <v>4.6</v>
+      </c>
+      <c r="AB146">
+        <v>1.49</v>
+      </c>
+      <c r="AC146">
+        <v>1.01</v>
+      </c>
+      <c r="AD146">
+        <v>17</v>
+      </c>
+      <c r="AE146">
+        <v>1.12</v>
+      </c>
+      <c r="AF146">
+        <v>6.5</v>
+      </c>
+      <c r="AG146">
+        <v>1.4</v>
+      </c>
+      <c r="AH146">
+        <v>2.9</v>
+      </c>
+      <c r="AI146">
+        <v>1.57</v>
+      </c>
+      <c r="AJ146">
+        <v>2.25</v>
+      </c>
+      <c r="AK146">
+        <v>2.65</v>
+      </c>
+      <c r="AL146">
+        <v>1.18</v>
+      </c>
+      <c r="AM146">
+        <v>1.13</v>
+      </c>
+      <c r="AN146">
+        <v>0.75</v>
+      </c>
+      <c r="AO146">
+        <v>0.71</v>
+      </c>
+      <c r="AP146">
+        <v>1</v>
+      </c>
+      <c r="AQ146">
+        <v>0.63</v>
+      </c>
+      <c r="AR146">
+        <v>1.19</v>
+      </c>
+      <c r="AS146">
+        <v>1.11</v>
+      </c>
+      <c r="AT146">
+        <v>2.3</v>
+      </c>
+      <c r="AU146">
+        <v>8</v>
+      </c>
+      <c r="AV146">
+        <v>5</v>
+      </c>
+      <c r="AW146">
+        <v>4</v>
+      </c>
+      <c r="AX146">
+        <v>12</v>
+      </c>
+      <c r="AY146">
+        <v>12</v>
+      </c>
+      <c r="AZ146">
+        <v>24</v>
+      </c>
+      <c r="BA146">
+        <v>1</v>
+      </c>
+      <c r="BB146">
+        <v>9</v>
+      </c>
+      <c r="BC146">
+        <v>10</v>
+      </c>
+      <c r="BD146">
+        <v>3.4</v>
+      </c>
+      <c r="BE146">
+        <v>7.5</v>
+      </c>
+      <c r="BF146">
+        <v>1.36</v>
+      </c>
+      <c r="BG146">
+        <v>1.21</v>
+      </c>
+      <c r="BH146">
+        <v>3.8</v>
+      </c>
+      <c r="BI146">
+        <v>1.38</v>
+      </c>
+      <c r="BJ146">
+        <v>2.75</v>
+      </c>
+      <c r="BK146">
+        <v>1.62</v>
+      </c>
+      <c r="BL146">
+        <v>2.14</v>
+      </c>
+      <c r="BM146">
+        <v>1.98</v>
+      </c>
+      <c r="BN146">
+        <v>1.72</v>
+      </c>
+      <c r="BO146">
+        <v>2.48</v>
+      </c>
+      <c r="BP146">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="147" spans="1:68">
+      <c r="A147" s="1">
+        <v>146</v>
+      </c>
+      <c r="B147">
+        <v>7491961</v>
+      </c>
+      <c r="C147" t="s">
+        <v>68</v>
+      </c>
+      <c r="D147" t="s">
+        <v>69</v>
+      </c>
+      <c r="E147" s="2">
+        <v>45671.6875</v>
+      </c>
+      <c r="F147">
+        <v>17</v>
+      </c>
+      <c r="G147" t="s">
+        <v>82</v>
+      </c>
+      <c r="H147" t="s">
+        <v>73</v>
+      </c>
+      <c r="I147">
+        <v>1</v>
+      </c>
+      <c r="J147">
+        <v>1</v>
+      </c>
+      <c r="K147">
+        <v>2</v>
+      </c>
+      <c r="L147">
+        <v>4</v>
+      </c>
+      <c r="M147">
+        <v>1</v>
+      </c>
+      <c r="N147">
+        <v>5</v>
+      </c>
+      <c r="O147" t="s">
+        <v>192</v>
+      </c>
+      <c r="P147" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q147">
+        <v>2.3</v>
+      </c>
+      <c r="R147">
+        <v>2.4</v>
+      </c>
+      <c r="S147">
+        <v>4.5</v>
+      </c>
+      <c r="T147">
+        <v>1.3</v>
+      </c>
+      <c r="U147">
+        <v>3.4</v>
+      </c>
+      <c r="V147">
+        <v>2.38</v>
+      </c>
+      <c r="W147">
+        <v>1.53</v>
+      </c>
+      <c r="X147">
+        <v>6</v>
+      </c>
+      <c r="Y147">
+        <v>1.13</v>
+      </c>
+      <c r="Z147">
+        <v>1.73</v>
+      </c>
+      <c r="AA147">
+        <v>4</v>
+      </c>
+      <c r="AB147">
+        <v>4.33</v>
+      </c>
+      <c r="AC147">
+        <v>1.02</v>
+      </c>
+      <c r="AD147">
+        <v>19</v>
+      </c>
+      <c r="AE147">
+        <v>1.19</v>
+      </c>
+      <c r="AF147">
+        <v>4.75</v>
+      </c>
+      <c r="AG147">
+        <v>1.57</v>
+      </c>
+      <c r="AH147">
+        <v>2.25</v>
+      </c>
+      <c r="AI147">
+        <v>1.62</v>
+      </c>
+      <c r="AJ147">
+        <v>2.2</v>
+      </c>
+      <c r="AK147">
+        <v>1.21</v>
+      </c>
+      <c r="AL147">
+        <v>1.24</v>
+      </c>
+      <c r="AM147">
+        <v>2.05</v>
+      </c>
+      <c r="AN147">
+        <v>2</v>
+      </c>
+      <c r="AO147">
+        <v>1</v>
+      </c>
+      <c r="AP147">
+        <v>2.13</v>
+      </c>
+      <c r="AQ147">
+        <v>0.89</v>
+      </c>
+      <c r="AR147">
+        <v>1.77</v>
+      </c>
+      <c r="AS147">
+        <v>1.25</v>
+      </c>
+      <c r="AT147">
+        <v>3.02</v>
+      </c>
+      <c r="AU147">
+        <v>9</v>
+      </c>
+      <c r="AV147">
+        <v>6</v>
+      </c>
+      <c r="AW147">
+        <v>15</v>
+      </c>
+      <c r="AX147">
+        <v>2</v>
+      </c>
+      <c r="AY147">
+        <v>30</v>
+      </c>
+      <c r="AZ147">
+        <v>9</v>
+      </c>
+      <c r="BA147">
+        <v>8</v>
+      </c>
+      <c r="BB147">
+        <v>1</v>
+      </c>
+      <c r="BC147">
+        <v>9</v>
+      </c>
+      <c r="BD147">
+        <v>1.49</v>
+      </c>
+      <c r="BE147">
+        <v>6.75</v>
+      </c>
+      <c r="BF147">
+        <v>2.95</v>
+      </c>
+      <c r="BG147">
+        <v>1.29</v>
+      </c>
+      <c r="BH147">
+        <v>3.15</v>
+      </c>
+      <c r="BI147">
+        <v>1.5</v>
+      </c>
+      <c r="BJ147">
+        <v>2.35</v>
+      </c>
+      <c r="BK147">
+        <v>1.82</v>
+      </c>
+      <c r="BL147">
+        <v>1.86</v>
+      </c>
+      <c r="BM147">
+        <v>2.28</v>
+      </c>
+      <c r="BN147">
+        <v>1.55</v>
+      </c>
+      <c r="BO147">
+        <v>2.9</v>
+      </c>
+      <c r="BP147">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="148" spans="1:68">
+      <c r="A148" s="1">
+        <v>147</v>
+      </c>
+      <c r="B148">
+        <v>7491963</v>
+      </c>
+      <c r="C148" t="s">
+        <v>68</v>
+      </c>
+      <c r="D148" t="s">
+        <v>69</v>
+      </c>
+      <c r="E148" s="2">
+        <v>45671.6875</v>
+      </c>
+      <c r="F148">
+        <v>17</v>
+      </c>
+      <c r="G148" t="s">
+        <v>77</v>
+      </c>
+      <c r="H148" t="s">
+        <v>70</v>
+      </c>
+      <c r="I148">
+        <v>1</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+      <c r="K148">
+        <v>1</v>
+      </c>
+      <c r="L148">
+        <v>5</v>
+      </c>
+      <c r="M148">
+        <v>1</v>
+      </c>
+      <c r="N148">
+        <v>6</v>
+      </c>
+      <c r="O148" t="s">
+        <v>193</v>
+      </c>
+      <c r="P148" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q148">
+        <v>2.5</v>
+      </c>
+      <c r="R148">
+        <v>2.4</v>
+      </c>
+      <c r="S148">
+        <v>3.75</v>
+      </c>
+      <c r="T148">
+        <v>1.29</v>
+      </c>
+      <c r="U148">
+        <v>3.5</v>
+      </c>
+      <c r="V148">
+        <v>2.25</v>
+      </c>
+      <c r="W148">
+        <v>1.57</v>
+      </c>
+      <c r="X148">
+        <v>5.5</v>
+      </c>
+      <c r="Y148">
+        <v>1.14</v>
+      </c>
+      <c r="Z148">
+        <v>2</v>
+      </c>
+      <c r="AA148">
+        <v>3.6</v>
+      </c>
+      <c r="AB148">
+        <v>3.6</v>
+      </c>
+      <c r="AC148">
+        <v>1.02</v>
+      </c>
+      <c r="AD148">
+        <v>19</v>
+      </c>
+      <c r="AE148">
+        <v>1.18</v>
+      </c>
+      <c r="AF148">
+        <v>5</v>
+      </c>
+      <c r="AG148">
+        <v>1.57</v>
+      </c>
+      <c r="AH148">
+        <v>2.35</v>
+      </c>
+      <c r="AI148">
+        <v>1.53</v>
+      </c>
+      <c r="AJ148">
+        <v>2.38</v>
+      </c>
+      <c r="AK148">
+        <v>1.29</v>
+      </c>
+      <c r="AL148">
+        <v>1.26</v>
+      </c>
+      <c r="AM148">
+        <v>1.8</v>
+      </c>
+      <c r="AN148">
+        <v>1</v>
+      </c>
+      <c r="AO148">
+        <v>1.14</v>
+      </c>
+      <c r="AP148">
+        <v>1.22</v>
+      </c>
+      <c r="AQ148">
+        <v>1</v>
+      </c>
+      <c r="AR148">
+        <v>1.3</v>
+      </c>
+      <c r="AS148">
+        <v>1.35</v>
+      </c>
+      <c r="AT148">
+        <v>2.65</v>
+      </c>
+      <c r="AU148">
+        <v>6</v>
+      </c>
+      <c r="AV148">
+        <v>6</v>
+      </c>
+      <c r="AW148">
+        <v>11</v>
+      </c>
+      <c r="AX148">
+        <v>4</v>
+      </c>
+      <c r="AY148">
+        <v>21</v>
+      </c>
+      <c r="AZ148">
+        <v>11</v>
+      </c>
+      <c r="BA148">
+        <v>4</v>
+      </c>
+      <c r="BB148">
+        <v>7</v>
+      </c>
+      <c r="BC148">
+        <v>11</v>
+      </c>
+      <c r="BD148">
+        <v>1.64</v>
+      </c>
+      <c r="BE148">
+        <v>6.4</v>
+      </c>
+      <c r="BF148">
+        <v>2.55</v>
+      </c>
+      <c r="BG148">
+        <v>1.27</v>
+      </c>
+      <c r="BH148">
+        <v>3.3</v>
+      </c>
+      <c r="BI148">
+        <v>1.47</v>
+      </c>
+      <c r="BJ148">
+        <v>2.43</v>
+      </c>
+      <c r="BK148">
+        <v>1.78</v>
+      </c>
+      <c r="BL148">
+        <v>1.91</v>
+      </c>
+      <c r="BM148">
+        <v>2.23</v>
+      </c>
+      <c r="BN148">
+        <v>1.57</v>
+      </c>
+      <c r="BO148">
+        <v>2.85</v>
+      </c>
+      <c r="BP148">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="149" spans="1:68">
+      <c r="A149" s="1">
+        <v>148</v>
+      </c>
+      <c r="B149">
+        <v>7491958</v>
+      </c>
+      <c r="C149" t="s">
+        <v>68</v>
+      </c>
+      <c r="D149" t="s">
+        <v>69</v>
+      </c>
+      <c r="E149" s="2">
+        <v>45671.6875</v>
+      </c>
+      <c r="F149">
+        <v>17</v>
+      </c>
+      <c r="G149" t="s">
+        <v>85</v>
+      </c>
+      <c r="H149" t="s">
+        <v>75</v>
+      </c>
+      <c r="I149">
+        <v>0</v>
+      </c>
+      <c r="J149">
+        <v>0</v>
+      </c>
+      <c r="K149">
+        <v>0</v>
+      </c>
+      <c r="L149">
+        <v>1</v>
+      </c>
+      <c r="M149">
+        <v>0</v>
+      </c>
+      <c r="N149">
+        <v>1</v>
+      </c>
+      <c r="O149" t="s">
+        <v>194</v>
+      </c>
+      <c r="P149" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q149">
+        <v>1.95</v>
+      </c>
+      <c r="R149">
+        <v>2.5</v>
+      </c>
+      <c r="S149">
+        <v>6</v>
+      </c>
+      <c r="T149">
+        <v>1.29</v>
+      </c>
+      <c r="U149">
+        <v>3.5</v>
+      </c>
+      <c r="V149">
+        <v>2.25</v>
+      </c>
+      <c r="W149">
+        <v>1.57</v>
+      </c>
+      <c r="X149">
+        <v>5.5</v>
+      </c>
+      <c r="Y149">
+        <v>1.14</v>
+      </c>
+      <c r="Z149">
+        <v>1.4</v>
+      </c>
+      <c r="AA149">
+        <v>4.8</v>
+      </c>
+      <c r="AB149">
+        <v>7.25</v>
+      </c>
+      <c r="AC149">
+        <v>1.02</v>
+      </c>
+      <c r="AD149">
+        <v>19</v>
+      </c>
+      <c r="AE149">
+        <v>1.18</v>
+      </c>
+      <c r="AF149">
+        <v>5</v>
+      </c>
+      <c r="AG149">
+        <v>1.57</v>
+      </c>
+      <c r="AH149">
+        <v>2.35</v>
+      </c>
+      <c r="AI149">
+        <v>1.75</v>
+      </c>
+      <c r="AJ149">
+        <v>2</v>
+      </c>
+      <c r="AK149">
+        <v>1.11</v>
+      </c>
+      <c r="AL149">
+        <v>1.19</v>
+      </c>
+      <c r="AM149">
+        <v>2.65</v>
+      </c>
+      <c r="AN149">
+        <v>2.13</v>
+      </c>
+      <c r="AO149">
+        <v>2</v>
+      </c>
+      <c r="AP149">
+        <v>2.22</v>
+      </c>
+      <c r="AQ149">
+        <v>1.75</v>
+      </c>
+      <c r="AR149">
+        <v>2.17</v>
+      </c>
+      <c r="AS149">
+        <v>1.17</v>
+      </c>
+      <c r="AT149">
+        <v>3.34</v>
+      </c>
+      <c r="AU149">
+        <v>10</v>
+      </c>
+      <c r="AV149">
+        <v>5</v>
+      </c>
+      <c r="AW149">
+        <v>11</v>
+      </c>
+      <c r="AX149">
+        <v>3</v>
+      </c>
+      <c r="AY149">
+        <v>30</v>
+      </c>
+      <c r="AZ149">
+        <v>9</v>
+      </c>
+      <c r="BA149">
+        <v>8</v>
+      </c>
+      <c r="BB149">
+        <v>4</v>
+      </c>
+      <c r="BC149">
+        <v>12</v>
+      </c>
+      <c r="BD149">
+        <v>1.24</v>
+      </c>
+      <c r="BE149">
+        <v>8</v>
+      </c>
+      <c r="BF149">
+        <v>4.4</v>
+      </c>
+      <c r="BG149">
+        <v>1.27</v>
+      </c>
+      <c r="BH149">
+        <v>3.3</v>
+      </c>
+      <c r="BI149">
+        <v>1.48</v>
+      </c>
+      <c r="BJ149">
+        <v>2.43</v>
+      </c>
+      <c r="BK149">
+        <v>1.77</v>
+      </c>
+      <c r="BL149">
+        <v>1.92</v>
+      </c>
+      <c r="BM149">
+        <v>2.2</v>
+      </c>
+      <c r="BN149">
+        <v>1.58</v>
+      </c>
+      <c r="BO149">
+        <v>2.8</v>
+      </c>
+      <c r="BP149">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="293">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -589,16 +589,25 @@
     <t>['23', '35', '47', '90']</t>
   </si>
   <si>
-    <t>['27', '32', '45+4', '90+8']</t>
+    <t>['27', '32', '45+4', '90+9']</t>
   </si>
   <si>
     <t>['43', '65', '71', '81']</t>
   </si>
   <si>
-    <t>['3', '60', '75', '83', '87']</t>
+    <t>['3', '60', '75', '84', '87']</t>
   </si>
   <si>
     <t>['48']</t>
+  </si>
+  <si>
+    <t>['50', '60']</t>
+  </si>
+  <si>
+    <t>['6', '12', '26', '48', '66']</t>
+  </si>
+  <si>
+    <t>['1', '56', '79']</t>
   </si>
   <si>
     <t>['12', '38', '90+11']</t>
@@ -874,7 +883,16 @@
     <t>['26', '90+3']</t>
   </si>
   <si>
-    <t>['71', '77']</t>
+    <t>['72', '78']</t>
+  </si>
+  <si>
+    <t>['10']</t>
+  </si>
+  <si>
+    <t>['30', '61', '90+5']</t>
+  </si>
+  <si>
+    <t>['8', '30']</t>
   </si>
 </sst>
 </file>
@@ -1236,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP149"/>
+  <dimension ref="A1:BP154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1492,7 +1510,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -1904,7 +1922,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2110,7 +2128,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2316,7 +2334,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2522,7 +2540,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2934,7 +2952,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3140,7 +3158,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3221,7 +3239,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ10">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3424,10 +3442,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ11">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3552,7 +3570,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3630,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ12">
         <v>1.75</v>
@@ -3758,7 +3776,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3964,7 +3982,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4045,7 +4063,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ14">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4170,7 +4188,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4248,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -4454,7 +4472,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ16">
         <v>0.63</v>
@@ -4582,7 +4600,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4663,7 +4681,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ17">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4869,7 +4887,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ18">
-        <v>0.29</v>
+        <v>0.63</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5072,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ19">
         <v>0.89</v>
@@ -5200,7 +5218,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5281,7 +5299,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ20">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR20">
         <v>1.89</v>
@@ -5612,7 +5630,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -6024,7 +6042,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6230,7 +6248,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6436,7 +6454,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -6642,7 +6660,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q27">
         <v>2.63</v>
@@ -6723,7 +6741,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ27">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR27">
         <v>1.22</v>
@@ -6848,7 +6866,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7054,7 +7072,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7260,7 +7278,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7466,7 +7484,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7544,7 +7562,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ31">
         <v>2.22</v>
@@ -7672,7 +7690,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7750,10 +7768,10 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ32">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR32">
         <v>1.36</v>
@@ -7878,7 +7896,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -7956,7 +7974,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ33">
         <v>0.25</v>
@@ -8290,7 +8308,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -8574,7 +8592,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ36">
         <v>0.63</v>
@@ -8783,7 +8801,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ37">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR37">
         <v>1.27</v>
@@ -8908,7 +8926,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9320,7 +9338,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9401,7 +9419,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ40">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR40">
         <v>1.48</v>
@@ -9526,7 +9544,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9732,7 +9750,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -9813,7 +9831,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ42">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR42">
         <v>1.82</v>
@@ -10019,7 +10037,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ43">
-        <v>0.29</v>
+        <v>0.63</v>
       </c>
       <c r="AR43">
         <v>1.14</v>
@@ -10144,7 +10162,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10222,7 +10240,7 @@
         <v>3</v>
       </c>
       <c r="AP44">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ44">
         <v>2.25</v>
@@ -10350,7 +10368,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10556,7 +10574,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10968,7 +10986,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11252,7 +11270,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ49">
         <v>0.89</v>
@@ -11380,7 +11398,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11458,7 +11476,7 @@
         <v>0.5</v>
       </c>
       <c r="AP50">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ50">
         <v>0.63</v>
@@ -11586,7 +11604,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -11664,7 +11682,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ51">
         <v>2</v>
@@ -11792,7 +11810,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12079,7 +12097,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ53">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR53">
         <v>1.25</v>
@@ -12204,7 +12222,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12410,7 +12428,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12488,10 +12506,10 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ55">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR55">
         <v>2.29</v>
@@ -12616,7 +12634,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -12697,7 +12715,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ56">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR56">
         <v>1.91</v>
@@ -12822,7 +12840,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -13234,7 +13252,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13315,7 +13333,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ59">
-        <v>0.29</v>
+        <v>0.63</v>
       </c>
       <c r="AR59">
         <v>1.71</v>
@@ -13440,7 +13458,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13521,7 +13539,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ60">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR60">
         <v>1.26</v>
@@ -13646,7 +13664,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -13727,7 +13745,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ61">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR61">
         <v>1.33</v>
@@ -13930,7 +13948,7 @@
         <v>1.33</v>
       </c>
       <c r="AP62">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ62">
         <v>1.5</v>
@@ -14058,7 +14076,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14264,7 +14282,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14470,7 +14488,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14676,7 +14694,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -15088,7 +15106,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15294,7 +15312,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q69">
         <v>1.8</v>
@@ -15372,7 +15390,7 @@
         <v>0.67</v>
       </c>
       <c r="AP69">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ69">
         <v>0.25</v>
@@ -15500,7 +15518,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15578,7 +15596,7 @@
         <v>2.33</v>
       </c>
       <c r="AP70">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ70">
         <v>2.25</v>
@@ -15706,7 +15724,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -15784,7 +15802,7 @@
         <v>2.5</v>
       </c>
       <c r="AP71">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ71">
         <v>2.22</v>
@@ -15912,7 +15930,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -15990,7 +16008,7 @@
         <v>1.5</v>
       </c>
       <c r="AP72">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ72">
         <v>1.78</v>
@@ -16199,7 +16217,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ73">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR73">
         <v>1.3</v>
@@ -16608,7 +16626,7 @@
         <v>1.25</v>
       </c>
       <c r="AP75">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ75">
         <v>0.5600000000000001</v>
@@ -16736,7 +16754,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -16942,7 +16960,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -17023,7 +17041,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ77">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR77">
         <v>1.67</v>
@@ -17229,7 +17247,7 @@
         <v>1</v>
       </c>
       <c r="AQ78">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR78">
         <v>1.15</v>
@@ -17435,7 +17453,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ79">
-        <v>0.29</v>
+        <v>0.63</v>
       </c>
       <c r="AR79">
         <v>1.14</v>
@@ -17641,7 +17659,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ80">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR80">
         <v>1.88</v>
@@ -18256,7 +18274,7 @@
         <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ83">
         <v>0.89</v>
@@ -18384,7 +18402,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18668,7 +18686,7 @@
         <v>0.5</v>
       </c>
       <c r="AP85">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ85">
         <v>0.25</v>
@@ -18796,7 +18814,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -19002,7 +19020,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19080,7 +19098,7 @@
         <v>2</v>
       </c>
       <c r="AP87">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ87">
         <v>2.25</v>
@@ -19495,7 +19513,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ89">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR89">
         <v>1.8</v>
@@ -19620,7 +19638,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19698,7 +19716,7 @@
         <v>1.4</v>
       </c>
       <c r="AP90">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ90">
         <v>1.78</v>
@@ -19826,7 +19844,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -20110,10 +20128,10 @@
         <v>0.25</v>
       </c>
       <c r="AP92">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ92">
-        <v>0.29</v>
+        <v>0.63</v>
       </c>
       <c r="AR92">
         <v>1.83</v>
@@ -20238,7 +20256,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -20319,7 +20337,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ93">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR93">
         <v>2.3</v>
@@ -20522,7 +20540,7 @@
         <v>0</v>
       </c>
       <c r="AP94">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ94">
         <v>0.11</v>
@@ -20856,7 +20874,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -20937,7 +20955,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ96">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR96">
         <v>1.68</v>
@@ -21474,7 +21492,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -21761,7 +21779,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ100">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR100">
         <v>1.65</v>
@@ -21886,7 +21904,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22092,7 +22110,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22170,7 +22188,7 @@
         <v>1.8</v>
       </c>
       <c r="AP102">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ102">
         <v>2.25</v>
@@ -22298,7 +22316,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22710,7 +22728,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -22916,7 +22934,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -22994,7 +23012,7 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ106">
         <v>1.5</v>
@@ -23122,7 +23140,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23409,7 +23427,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ108">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR108">
         <v>1.45</v>
@@ -23534,7 +23552,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -23740,7 +23758,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -23818,7 +23836,7 @@
         <v>0.83</v>
       </c>
       <c r="AP110">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ110">
         <v>0.5600000000000001</v>
@@ -23946,7 +23964,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24027,7 +24045,7 @@
         <v>1</v>
       </c>
       <c r="AQ111">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR111">
         <v>1.13</v>
@@ -24152,7 +24170,7 @@
         <v>96</v>
       </c>
       <c r="P112" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q112">
         <v>3.4</v>
@@ -24230,7 +24248,7 @@
         <v>1.67</v>
       </c>
       <c r="AP112">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ112">
         <v>1.78</v>
@@ -24358,7 +24376,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24439,7 +24457,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ113">
-        <v>0.29</v>
+        <v>0.63</v>
       </c>
       <c r="AR113">
         <v>1.55</v>
@@ -24564,7 +24582,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -24642,10 +24660,10 @@
         <v>1</v>
       </c>
       <c r="AP114">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ114">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR114">
         <v>2.04</v>
@@ -24770,7 +24788,7 @@
         <v>169</v>
       </c>
       <c r="P115" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q115">
         <v>1.62</v>
@@ -24851,7 +24869,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ115">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR115">
         <v>2.31</v>
@@ -24976,7 +24994,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25182,7 +25200,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25388,7 +25406,7 @@
         <v>171</v>
       </c>
       <c r="P118" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25594,7 +25612,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -25800,7 +25818,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -25878,7 +25896,7 @@
         <v>0</v>
       </c>
       <c r="AP120">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ120">
         <v>0.11</v>
@@ -26006,7 +26024,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26212,7 +26230,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26418,7 +26436,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q123">
         <v>1.91</v>
@@ -26624,7 +26642,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26830,7 +26848,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -27036,7 +27054,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27117,7 +27135,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ126">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR126">
         <v>1.74</v>
@@ -27242,7 +27260,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27448,7 +27466,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27526,10 +27544,10 @@
         <v>1.86</v>
       </c>
       <c r="AP128">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ128">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR128">
         <v>2.15</v>
@@ -27654,7 +27672,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27735,7 +27753,7 @@
         <v>1</v>
       </c>
       <c r="AQ129">
-        <v>0.29</v>
+        <v>0.63</v>
       </c>
       <c r="AR129">
         <v>1.19</v>
@@ -27860,7 +27878,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -27938,10 +27956,10 @@
         <v>0.86</v>
       </c>
       <c r="AP130">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ130">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR130">
         <v>1.98</v>
@@ -28066,7 +28084,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28272,7 +28290,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28478,7 +28496,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28556,7 +28574,7 @@
         <v>0.71</v>
       </c>
       <c r="AP133">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ133">
         <v>0.5600000000000001</v>
@@ -28968,10 +28986,10 @@
         <v>0.86</v>
       </c>
       <c r="AP135">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ135">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR135">
         <v>1.23</v>
@@ -29096,7 +29114,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29302,7 +29320,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -29920,7 +29938,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q140">
         <v>1.83</v>
@@ -30332,7 +30350,7 @@
         <v>96</v>
       </c>
       <c r="P142" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30538,7 +30556,7 @@
         <v>96</v>
       </c>
       <c r="P143" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -30744,7 +30762,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -30950,7 +30968,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31156,7 +31174,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31931,6 +31949,1036 @@
       </c>
       <c r="BP149">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="150" spans="1:68">
+      <c r="A150" s="1">
+        <v>149</v>
+      </c>
+      <c r="B150">
+        <v>7491965</v>
+      </c>
+      <c r="C150" t="s">
+        <v>68</v>
+      </c>
+      <c r="D150" t="s">
+        <v>69</v>
+      </c>
+      <c r="E150" s="2">
+        <v>45672.60416666666</v>
+      </c>
+      <c r="F150">
+        <v>17</v>
+      </c>
+      <c r="G150" t="s">
+        <v>83</v>
+      </c>
+      <c r="H150" t="s">
+        <v>78</v>
+      </c>
+      <c r="I150">
+        <v>0</v>
+      </c>
+      <c r="J150">
+        <v>0</v>
+      </c>
+      <c r="K150">
+        <v>0</v>
+      </c>
+      <c r="L150">
+        <v>1</v>
+      </c>
+      <c r="M150">
+        <v>0</v>
+      </c>
+      <c r="N150">
+        <v>1</v>
+      </c>
+      <c r="O150" t="s">
+        <v>141</v>
+      </c>
+      <c r="P150" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q150">
+        <v>3.1</v>
+      </c>
+      <c r="R150">
+        <v>2.1</v>
+      </c>
+      <c r="S150">
+        <v>3.4</v>
+      </c>
+      <c r="T150">
+        <v>1.4</v>
+      </c>
+      <c r="U150">
+        <v>2.75</v>
+      </c>
+      <c r="V150">
+        <v>3</v>
+      </c>
+      <c r="W150">
+        <v>1.36</v>
+      </c>
+      <c r="X150">
+        <v>8</v>
+      </c>
+      <c r="Y150">
+        <v>1.08</v>
+      </c>
+      <c r="Z150">
+        <v>2.32</v>
+      </c>
+      <c r="AA150">
+        <v>3.12</v>
+      </c>
+      <c r="AB150">
+        <v>2.63</v>
+      </c>
+      <c r="AC150">
+        <v>1.06</v>
+      </c>
+      <c r="AD150">
+        <v>10</v>
+      </c>
+      <c r="AE150">
+        <v>1.36</v>
+      </c>
+      <c r="AF150">
+        <v>3.2</v>
+      </c>
+      <c r="AG150">
+        <v>1.9</v>
+      </c>
+      <c r="AH150">
+        <v>1.96</v>
+      </c>
+      <c r="AI150">
+        <v>1.75</v>
+      </c>
+      <c r="AJ150">
+        <v>2</v>
+      </c>
+      <c r="AK150">
+        <v>1.42</v>
+      </c>
+      <c r="AL150">
+        <v>1.32</v>
+      </c>
+      <c r="AM150">
+        <v>1.5</v>
+      </c>
+      <c r="AN150">
+        <v>0.71</v>
+      </c>
+      <c r="AO150">
+        <v>1.13</v>
+      </c>
+      <c r="AP150">
+        <v>1</v>
+      </c>
+      <c r="AQ150">
+        <v>1</v>
+      </c>
+      <c r="AR150">
+        <v>1.25</v>
+      </c>
+      <c r="AS150">
+        <v>1.13</v>
+      </c>
+      <c r="AT150">
+        <v>2.38</v>
+      </c>
+      <c r="AU150">
+        <v>2</v>
+      </c>
+      <c r="AV150">
+        <v>3</v>
+      </c>
+      <c r="AW150">
+        <v>8</v>
+      </c>
+      <c r="AX150">
+        <v>11</v>
+      </c>
+      <c r="AY150">
+        <v>13</v>
+      </c>
+      <c r="AZ150">
+        <v>18</v>
+      </c>
+      <c r="BA150">
+        <v>6</v>
+      </c>
+      <c r="BB150">
+        <v>7</v>
+      </c>
+      <c r="BC150">
+        <v>13</v>
+      </c>
+      <c r="BD150">
+        <v>1.88</v>
+      </c>
+      <c r="BE150">
+        <v>6.4</v>
+      </c>
+      <c r="BF150">
+        <v>2.15</v>
+      </c>
+      <c r="BG150">
+        <v>1.24</v>
+      </c>
+      <c r="BH150">
+        <v>3.7</v>
+      </c>
+      <c r="BI150">
+        <v>1.44</v>
+      </c>
+      <c r="BJ150">
+        <v>2.55</v>
+      </c>
+      <c r="BK150">
+        <v>1.78</v>
+      </c>
+      <c r="BL150">
+        <v>1.9</v>
+      </c>
+      <c r="BM150">
+        <v>2.35</v>
+      </c>
+      <c r="BN150">
+        <v>1.52</v>
+      </c>
+      <c r="BO150">
+        <v>3.25</v>
+      </c>
+      <c r="BP150">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="151" spans="1:68">
+      <c r="A151" s="1">
+        <v>150</v>
+      </c>
+      <c r="B151">
+        <v>7491959</v>
+      </c>
+      <c r="C151" t="s">
+        <v>68</v>
+      </c>
+      <c r="D151" t="s">
+        <v>69</v>
+      </c>
+      <c r="E151" s="2">
+        <v>45672.6875</v>
+      </c>
+      <c r="F151">
+        <v>17</v>
+      </c>
+      <c r="G151" t="s">
+        <v>80</v>
+      </c>
+      <c r="H151" t="s">
+        <v>71</v>
+      </c>
+      <c r="I151">
+        <v>0</v>
+      </c>
+      <c r="J151">
+        <v>1</v>
+      </c>
+      <c r="K151">
+        <v>1</v>
+      </c>
+      <c r="L151">
+        <v>2</v>
+      </c>
+      <c r="M151">
+        <v>1</v>
+      </c>
+      <c r="N151">
+        <v>3</v>
+      </c>
+      <c r="O151" t="s">
+        <v>195</v>
+      </c>
+      <c r="P151" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q151">
+        <v>2.6</v>
+      </c>
+      <c r="R151">
+        <v>2.5</v>
+      </c>
+      <c r="S151">
+        <v>3.4</v>
+      </c>
+      <c r="T151">
+        <v>1.25</v>
+      </c>
+      <c r="U151">
+        <v>3.75</v>
+      </c>
+      <c r="V151">
+        <v>2.2</v>
+      </c>
+      <c r="W151">
+        <v>1.62</v>
+      </c>
+      <c r="X151">
+        <v>5</v>
+      </c>
+      <c r="Y151">
+        <v>1.17</v>
+      </c>
+      <c r="Z151">
+        <v>1.95</v>
+      </c>
+      <c r="AA151">
+        <v>3.58</v>
+      </c>
+      <c r="AB151">
+        <v>2.96</v>
+      </c>
+      <c r="AC151">
+        <v>1.02</v>
+      </c>
+      <c r="AD151">
+        <v>19</v>
+      </c>
+      <c r="AE151">
+        <v>1.15</v>
+      </c>
+      <c r="AF151">
+        <v>5.5</v>
+      </c>
+      <c r="AG151">
+        <v>1.44</v>
+      </c>
+      <c r="AH151">
+        <v>2.75</v>
+      </c>
+      <c r="AI151">
+        <v>1.44</v>
+      </c>
+      <c r="AJ151">
+        <v>2.63</v>
+      </c>
+      <c r="AK151">
+        <v>1.36</v>
+      </c>
+      <c r="AL151">
+        <v>1.26</v>
+      </c>
+      <c r="AM151">
+        <v>1.68</v>
+      </c>
+      <c r="AN151">
+        <v>1.75</v>
+      </c>
+      <c r="AO151">
+        <v>1.63</v>
+      </c>
+      <c r="AP151">
+        <v>1.89</v>
+      </c>
+      <c r="AQ151">
+        <v>1.44</v>
+      </c>
+      <c r="AR151">
+        <v>1.96</v>
+      </c>
+      <c r="AS151">
+        <v>1.12</v>
+      </c>
+      <c r="AT151">
+        <v>3.08</v>
+      </c>
+      <c r="AU151">
+        <v>7</v>
+      </c>
+      <c r="AV151">
+        <v>4</v>
+      </c>
+      <c r="AW151">
+        <v>8</v>
+      </c>
+      <c r="AX151">
+        <v>3</v>
+      </c>
+      <c r="AY151">
+        <v>17</v>
+      </c>
+      <c r="AZ151">
+        <v>9</v>
+      </c>
+      <c r="BA151">
+        <v>5</v>
+      </c>
+      <c r="BB151">
+        <v>0</v>
+      </c>
+      <c r="BC151">
+        <v>5</v>
+      </c>
+      <c r="BD151">
+        <v>1.68</v>
+      </c>
+      <c r="BE151">
+        <v>6.4</v>
+      </c>
+      <c r="BF151">
+        <v>2.45</v>
+      </c>
+      <c r="BG151">
+        <v>1.24</v>
+      </c>
+      <c r="BH151">
+        <v>3.7</v>
+      </c>
+      <c r="BI151">
+        <v>1.44</v>
+      </c>
+      <c r="BJ151">
+        <v>2.55</v>
+      </c>
+      <c r="BK151">
+        <v>1.78</v>
+      </c>
+      <c r="BL151">
+        <v>1.9</v>
+      </c>
+      <c r="BM151">
+        <v>2.3</v>
+      </c>
+      <c r="BN151">
+        <v>1.53</v>
+      </c>
+      <c r="BO151">
+        <v>3.2</v>
+      </c>
+      <c r="BP151">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:68">
+      <c r="A152" s="1">
+        <v>151</v>
+      </c>
+      <c r="B152">
+        <v>7491960</v>
+      </c>
+      <c r="C152" t="s">
+        <v>68</v>
+      </c>
+      <c r="D152" t="s">
+        <v>69</v>
+      </c>
+      <c r="E152" s="2">
+        <v>45672.6875</v>
+      </c>
+      <c r="F152">
+        <v>17</v>
+      </c>
+      <c r="G152" t="s">
+        <v>87</v>
+      </c>
+      <c r="H152" t="s">
+        <v>72</v>
+      </c>
+      <c r="I152">
+        <v>3</v>
+      </c>
+      <c r="J152">
+        <v>0</v>
+      </c>
+      <c r="K152">
+        <v>3</v>
+      </c>
+      <c r="L152">
+        <v>5</v>
+      </c>
+      <c r="M152">
+        <v>0</v>
+      </c>
+      <c r="N152">
+        <v>5</v>
+      </c>
+      <c r="O152" t="s">
+        <v>196</v>
+      </c>
+      <c r="P152" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q152">
+        <v>1.44</v>
+      </c>
+      <c r="R152">
+        <v>3.5</v>
+      </c>
+      <c r="S152">
+        <v>10</v>
+      </c>
+      <c r="T152">
+        <v>1.14</v>
+      </c>
+      <c r="U152">
+        <v>5.5</v>
+      </c>
+      <c r="V152">
+        <v>1.73</v>
+      </c>
+      <c r="W152">
+        <v>2</v>
+      </c>
+      <c r="X152">
+        <v>3.25</v>
+      </c>
+      <c r="Y152">
+        <v>1.33</v>
+      </c>
+      <c r="Z152">
+        <v>1.12</v>
+      </c>
+      <c r="AA152">
+        <v>7.53</v>
+      </c>
+      <c r="AB152">
+        <v>11.56</v>
+      </c>
+      <c r="AC152">
+        <v>0</v>
+      </c>
+      <c r="AD152">
+        <v>0</v>
+      </c>
+      <c r="AE152">
+        <v>1.05</v>
+      </c>
+      <c r="AF152">
+        <v>10</v>
+      </c>
+      <c r="AG152">
+        <v>1.22</v>
+      </c>
+      <c r="AH152">
+        <v>4.2</v>
+      </c>
+      <c r="AI152">
+        <v>1.75</v>
+      </c>
+      <c r="AJ152">
+        <v>2</v>
+      </c>
+      <c r="AK152">
+        <v>1.02</v>
+      </c>
+      <c r="AL152">
+        <v>1.06</v>
+      </c>
+      <c r="AM152">
+        <v>6</v>
+      </c>
+      <c r="AN152">
+        <v>2.71</v>
+      </c>
+      <c r="AO152">
+        <v>0.57</v>
+      </c>
+      <c r="AP152">
+        <v>2.75</v>
+      </c>
+      <c r="AQ152">
+        <v>0.5</v>
+      </c>
+      <c r="AR152">
+        <v>2.19</v>
+      </c>
+      <c r="AS152">
+        <v>1.11</v>
+      </c>
+      <c r="AT152">
+        <v>3.3</v>
+      </c>
+      <c r="AU152">
+        <v>11</v>
+      </c>
+      <c r="AV152">
+        <v>3</v>
+      </c>
+      <c r="AW152">
+        <v>15</v>
+      </c>
+      <c r="AX152">
+        <v>3</v>
+      </c>
+      <c r="AY152">
+        <v>35</v>
+      </c>
+      <c r="AZ152">
+        <v>6</v>
+      </c>
+      <c r="BA152">
+        <v>13</v>
+      </c>
+      <c r="BB152">
+        <v>1</v>
+      </c>
+      <c r="BC152">
+        <v>14</v>
+      </c>
+      <c r="BD152">
+        <v>1.05</v>
+      </c>
+      <c r="BE152">
+        <v>14</v>
+      </c>
+      <c r="BF152">
+        <v>11</v>
+      </c>
+      <c r="BG152">
+        <v>1.17</v>
+      </c>
+      <c r="BH152">
+        <v>4.6</v>
+      </c>
+      <c r="BI152">
+        <v>1.32</v>
+      </c>
+      <c r="BJ152">
+        <v>3.1</v>
+      </c>
+      <c r="BK152">
+        <v>1.58</v>
+      </c>
+      <c r="BL152">
+        <v>2.2</v>
+      </c>
+      <c r="BM152">
+        <v>1.98</v>
+      </c>
+      <c r="BN152">
+        <v>1.72</v>
+      </c>
+      <c r="BO152">
+        <v>2.6</v>
+      </c>
+      <c r="BP152">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="153" spans="1:68">
+      <c r="A153" s="1">
+        <v>152</v>
+      </c>
+      <c r="B153">
+        <v>7491962</v>
+      </c>
+      <c r="C153" t="s">
+        <v>68</v>
+      </c>
+      <c r="D153" t="s">
+        <v>69</v>
+      </c>
+      <c r="E153" s="2">
+        <v>45672.6875</v>
+      </c>
+      <c r="F153">
+        <v>17</v>
+      </c>
+      <c r="G153" t="s">
+        <v>84</v>
+      </c>
+      <c r="H153" t="s">
+        <v>86</v>
+      </c>
+      <c r="I153">
+        <v>1</v>
+      </c>
+      <c r="J153">
+        <v>1</v>
+      </c>
+      <c r="K153">
+        <v>2</v>
+      </c>
+      <c r="L153">
+        <v>3</v>
+      </c>
+      <c r="M153">
+        <v>3</v>
+      </c>
+      <c r="N153">
+        <v>6</v>
+      </c>
+      <c r="O153" t="s">
+        <v>197</v>
+      </c>
+      <c r="P153" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q153">
+        <v>2.1</v>
+      </c>
+      <c r="R153">
+        <v>2.4</v>
+      </c>
+      <c r="S153">
+        <v>5</v>
+      </c>
+      <c r="T153">
+        <v>1.3</v>
+      </c>
+      <c r="U153">
+        <v>3.4</v>
+      </c>
+      <c r="V153">
+        <v>2.38</v>
+      </c>
+      <c r="W153">
+        <v>1.53</v>
+      </c>
+      <c r="X153">
+        <v>6</v>
+      </c>
+      <c r="Y153">
+        <v>1.13</v>
+      </c>
+      <c r="Z153">
+        <v>1.49</v>
+      </c>
+      <c r="AA153">
+        <v>3.98</v>
+      </c>
+      <c r="AB153">
+        <v>4.84</v>
+      </c>
+      <c r="AC153">
+        <v>1.02</v>
+      </c>
+      <c r="AD153">
+        <v>17</v>
+      </c>
+      <c r="AE153">
+        <v>1.2</v>
+      </c>
+      <c r="AF153">
+        <v>4.5</v>
+      </c>
+      <c r="AG153">
+        <v>1.6</v>
+      </c>
+      <c r="AH153">
+        <v>2.3</v>
+      </c>
+      <c r="AI153">
+        <v>1.67</v>
+      </c>
+      <c r="AJ153">
+        <v>2.1</v>
+      </c>
+      <c r="AK153">
+        <v>1.17</v>
+      </c>
+      <c r="AL153">
+        <v>1.22</v>
+      </c>
+      <c r="AM153">
+        <v>2.25</v>
+      </c>
+      <c r="AN153">
+        <v>1.29</v>
+      </c>
+      <c r="AO153">
+        <v>0.75</v>
+      </c>
+      <c r="AP153">
+        <v>1.25</v>
+      </c>
+      <c r="AQ153">
+        <v>0.78</v>
+      </c>
+      <c r="AR153">
+        <v>1.26</v>
+      </c>
+      <c r="AS153">
+        <v>1.13</v>
+      </c>
+      <c r="AT153">
+        <v>2.39</v>
+      </c>
+      <c r="AU153">
+        <v>6</v>
+      </c>
+      <c r="AV153">
+        <v>6</v>
+      </c>
+      <c r="AW153">
+        <v>7</v>
+      </c>
+      <c r="AX153">
+        <v>9</v>
+      </c>
+      <c r="AY153">
+        <v>16</v>
+      </c>
+      <c r="AZ153">
+        <v>17</v>
+      </c>
+      <c r="BA153">
+        <v>4</v>
+      </c>
+      <c r="BB153">
+        <v>2</v>
+      </c>
+      <c r="BC153">
+        <v>6</v>
+      </c>
+      <c r="BD153">
+        <v>1.5</v>
+      </c>
+      <c r="BE153">
+        <v>6.75</v>
+      </c>
+      <c r="BF153">
+        <v>2.9</v>
+      </c>
+      <c r="BG153">
+        <v>1.26</v>
+      </c>
+      <c r="BH153">
+        <v>3.5</v>
+      </c>
+      <c r="BI153">
+        <v>1.49</v>
+      </c>
+      <c r="BJ153">
+        <v>2.4</v>
+      </c>
+      <c r="BK153">
+        <v>1.87</v>
+      </c>
+      <c r="BL153">
+        <v>1.82</v>
+      </c>
+      <c r="BM153">
+        <v>2.45</v>
+      </c>
+      <c r="BN153">
+        <v>1.47</v>
+      </c>
+      <c r="BO153">
+        <v>3.4</v>
+      </c>
+      <c r="BP153">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="154" spans="1:68">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154">
+        <v>7491964</v>
+      </c>
+      <c r="C154" t="s">
+        <v>68</v>
+      </c>
+      <c r="D154" t="s">
+        <v>69</v>
+      </c>
+      <c r="E154" s="2">
+        <v>45672.6875</v>
+      </c>
+      <c r="F154">
+        <v>17</v>
+      </c>
+      <c r="G154" t="s">
+        <v>79</v>
+      </c>
+      <c r="H154" t="s">
+        <v>74</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+      <c r="J154">
+        <v>2</v>
+      </c>
+      <c r="K154">
+        <v>2</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
+      </c>
+      <c r="M154">
+        <v>2</v>
+      </c>
+      <c r="N154">
+        <v>2</v>
+      </c>
+      <c r="O154" t="s">
+        <v>96</v>
+      </c>
+      <c r="P154" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q154">
+        <v>2.6</v>
+      </c>
+      <c r="R154">
+        <v>2.1</v>
+      </c>
+      <c r="S154">
+        <v>4.75</v>
+      </c>
+      <c r="T154">
+        <v>1.44</v>
+      </c>
+      <c r="U154">
+        <v>2.63</v>
+      </c>
+      <c r="V154">
+        <v>3.25</v>
+      </c>
+      <c r="W154">
+        <v>1.33</v>
+      </c>
+      <c r="X154">
+        <v>9</v>
+      </c>
+      <c r="Y154">
+        <v>1.07</v>
+      </c>
+      <c r="Z154">
+        <v>1.88</v>
+      </c>
+      <c r="AA154">
+        <v>3.14</v>
+      </c>
+      <c r="AB154">
+        <v>3.59</v>
+      </c>
+      <c r="AC154">
+        <v>1.07</v>
+      </c>
+      <c r="AD154">
+        <v>9.5</v>
+      </c>
+      <c r="AE154">
+        <v>1.38</v>
+      </c>
+      <c r="AF154">
+        <v>3.1</v>
+      </c>
+      <c r="AG154">
+        <v>2.05</v>
+      </c>
+      <c r="AH154">
+        <v>1.75</v>
+      </c>
+      <c r="AI154">
+        <v>1.95</v>
+      </c>
+      <c r="AJ154">
+        <v>1.8</v>
+      </c>
+      <c r="AK154">
+        <v>1.21</v>
+      </c>
+      <c r="AL154">
+        <v>1.31</v>
+      </c>
+      <c r="AM154">
+        <v>1.87</v>
+      </c>
+      <c r="AN154">
+        <v>1.71</v>
+      </c>
+      <c r="AO154">
+        <v>0.29</v>
+      </c>
+      <c r="AP154">
+        <v>1.5</v>
+      </c>
+      <c r="AQ154">
+        <v>0.63</v>
+      </c>
+      <c r="AR154">
+        <v>1.41</v>
+      </c>
+      <c r="AS154">
+        <v>0.95</v>
+      </c>
+      <c r="AT154">
+        <v>2.36</v>
+      </c>
+      <c r="AU154">
+        <v>3</v>
+      </c>
+      <c r="AV154">
+        <v>6</v>
+      </c>
+      <c r="AW154">
+        <v>11</v>
+      </c>
+      <c r="AX154">
+        <v>6</v>
+      </c>
+      <c r="AY154">
+        <v>17</v>
+      </c>
+      <c r="AZ154">
+        <v>16</v>
+      </c>
+      <c r="BA154">
+        <v>7</v>
+      </c>
+      <c r="BB154">
+        <v>4</v>
+      </c>
+      <c r="BC154">
+        <v>11</v>
+      </c>
+      <c r="BD154">
+        <v>1.54</v>
+      </c>
+      <c r="BE154">
+        <v>6.75</v>
+      </c>
+      <c r="BF154">
+        <v>2.7</v>
+      </c>
+      <c r="BG154">
+        <v>1.21</v>
+      </c>
+      <c r="BH154">
+        <v>4</v>
+      </c>
+      <c r="BI154">
+        <v>1.39</v>
+      </c>
+      <c r="BJ154">
+        <v>2.75</v>
+      </c>
+      <c r="BK154">
+        <v>1.7</v>
+      </c>
+      <c r="BL154">
+        <v>2</v>
+      </c>
+      <c r="BM154">
+        <v>2.2</v>
+      </c>
+      <c r="BN154">
+        <v>1.6</v>
+      </c>
+      <c r="BO154">
+        <v>3</v>
+      </c>
+      <c r="BP154">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="302">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -610,6 +610,24 @@
     <t>['1', '56', '79']</t>
   </si>
   <si>
+    <t>['18', '90+2']</t>
+  </si>
+  <si>
+    <t>['84']</t>
+  </si>
+  <si>
+    <t>['48', '56', '61']</t>
+  </si>
+  <si>
+    <t>['2', '17', '45+5', '80']</t>
+  </si>
+  <si>
+    <t>['20', '39', '62']</t>
+  </si>
+  <si>
+    <t>['32', '62', '74']</t>
+  </si>
+  <si>
     <t>['12', '38', '90+11']</t>
   </si>
   <si>
@@ -751,9 +769,6 @@
     <t>['15']</t>
   </si>
   <si>
-    <t>['84']</t>
-  </si>
-  <si>
     <t>['30', '77']</t>
   </si>
   <si>
@@ -893,6 +908,18 @@
   </si>
   <si>
     <t>['8', '30']</t>
+  </si>
+  <si>
+    <t>['26', '45+1', '56']</t>
+  </si>
+  <si>
+    <t>['10', '13', '21']</t>
+  </si>
+  <si>
+    <t>['25', '90+2']</t>
+  </si>
+  <si>
+    <t>['24', '88']</t>
   </si>
 </sst>
 </file>
@@ -1254,7 +1281,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP154"/>
+  <dimension ref="A1:BP161"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1510,7 +1537,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -1922,7 +1949,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2128,7 +2155,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2334,7 +2361,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2540,7 +2567,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2952,7 +2979,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3158,7 +3185,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3445,7 +3472,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ11">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3570,7 +3597,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3648,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ12">
         <v>1.75</v>
@@ -3776,7 +3803,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -3854,10 +3881,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ13">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3982,7 +4009,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4060,10 +4087,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ14">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4188,7 +4215,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4269,7 +4296,7 @@
         <v>1</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4475,7 +4502,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ16">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4600,7 +4627,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4678,10 +4705,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ17">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4884,7 +4911,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ18">
         <v>0.63</v>
@@ -5090,10 +5117,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ19">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5218,7 +5245,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5630,7 +5657,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -6042,7 +6069,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6248,7 +6275,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6454,7 +6481,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -6532,7 +6559,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ26">
         <v>2.22</v>
@@ -6660,7 +6687,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="Q27">
         <v>2.63</v>
@@ -6741,7 +6768,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ27">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR27">
         <v>1.22</v>
@@ -6866,7 +6893,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7072,7 +7099,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7278,7 +7305,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7356,10 +7383,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ30">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR30">
         <v>1.69</v>
@@ -7484,7 +7511,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7690,7 +7717,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7771,7 +7798,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ32">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR32">
         <v>1.36</v>
@@ -7896,7 +7923,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8180,10 +8207,10 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ34">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR34">
         <v>1.86</v>
@@ -8308,7 +8335,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -8386,10 +8413,10 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ35">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR35">
         <v>2.58</v>
@@ -8592,10 +8619,10 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ36">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR36">
         <v>2.62</v>
@@ -8801,7 +8828,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ37">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR37">
         <v>1.27</v>
@@ -8926,7 +8953,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9338,7 +9365,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9544,7 +9571,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9750,7 +9777,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -9831,7 +9858,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ42">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR42">
         <v>1.82</v>
@@ -10162,7 +10189,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10240,7 +10267,7 @@
         <v>3</v>
       </c>
       <c r="AP44">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ44">
         <v>2.25</v>
@@ -10368,7 +10395,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10446,7 +10473,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ45">
         <v>1.78</v>
@@ -10574,7 +10601,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -10861,7 +10888,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ47">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR47">
         <v>2.02</v>
@@ -10986,7 +11013,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11064,7 +11091,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ48">
         <v>0.25</v>
@@ -11273,7 +11300,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ49">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR49">
         <v>0.41</v>
@@ -11398,7 +11425,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11479,7 +11506,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ50">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR50">
         <v>1.16</v>
@@ -11604,7 +11631,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -11685,7 +11712,7 @@
         <v>1</v>
       </c>
       <c r="AQ51">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR51">
         <v>1.37</v>
@@ -11810,7 +11837,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12094,10 +12121,10 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ53">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR53">
         <v>1.25</v>
@@ -12222,7 +12249,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12300,7 +12327,7 @@
         <v>3</v>
       </c>
       <c r="AP54">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ54">
         <v>2.22</v>
@@ -12428,7 +12455,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12506,10 +12533,10 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ55">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR55">
         <v>2.29</v>
@@ -12634,7 +12661,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -12715,7 +12742,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ56">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR56">
         <v>1.91</v>
@@ -12840,7 +12867,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -12918,7 +12945,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ57">
         <v>1.78</v>
@@ -13252,7 +13279,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13458,7 +13485,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13539,7 +13566,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ60">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR60">
         <v>1.26</v>
@@ -13664,7 +13691,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -13948,7 +13975,7 @@
         <v>1.33</v>
       </c>
       <c r="AP62">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ62">
         <v>1.5</v>
@@ -14076,7 +14103,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14154,7 +14181,7 @@
         <v>0.67</v>
       </c>
       <c r="AP63">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ63">
         <v>0.5600000000000001</v>
@@ -14282,7 +14309,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14488,7 +14515,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14569,7 +14596,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ65">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR65">
         <v>1.22</v>
@@ -14694,7 +14721,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14775,7 +14802,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ66">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR66">
         <v>1.91</v>
@@ -14981,7 +15008,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ67">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR67">
         <v>1.52</v>
@@ -15106,7 +15133,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15187,7 +15214,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ68">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR68">
         <v>1.33</v>
@@ -15312,7 +15339,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>245</v>
+        <v>199</v>
       </c>
       <c r="Q69">
         <v>1.8</v>
@@ -15390,7 +15417,7 @@
         <v>0.67</v>
       </c>
       <c r="AP69">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ69">
         <v>0.25</v>
@@ -15518,7 +15545,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15724,7 +15751,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -15930,7 +15957,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16214,10 +16241,10 @@
         <v>0.33</v>
       </c>
       <c r="AP73">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ73">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR73">
         <v>1.3</v>
@@ -16420,7 +16447,7 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ74">
         <v>1.5</v>
@@ -16626,7 +16653,7 @@
         <v>1.25</v>
       </c>
       <c r="AP75">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ75">
         <v>0.5600000000000001</v>
@@ -16754,7 +16781,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -16832,7 +16859,7 @@
         <v>0</v>
       </c>
       <c r="AP76">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ76">
         <v>0.11</v>
@@ -16960,7 +16987,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -17041,7 +17068,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ77">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR77">
         <v>1.67</v>
@@ -17244,7 +17271,7 @@
         <v>1.5</v>
       </c>
       <c r="AP78">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ78">
         <v>0.78</v>
@@ -17659,7 +17686,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ80">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR80">
         <v>1.88</v>
@@ -18277,7 +18304,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ83">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR83">
         <v>1.3</v>
@@ -18402,7 +18429,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18814,7 +18841,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -18895,7 +18922,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ86">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR86">
         <v>1.34</v>
@@ -19020,7 +19047,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19307,7 +19334,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ88">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR88">
         <v>1.44</v>
@@ -19513,7 +19540,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ89">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR89">
         <v>1.8</v>
@@ -19638,7 +19665,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19716,7 +19743,7 @@
         <v>1.4</v>
       </c>
       <c r="AP90">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ90">
         <v>1.78</v>
@@ -19844,7 +19871,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -19922,10 +19949,10 @@
         <v>1.75</v>
       </c>
       <c r="AP91">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ91">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR91">
         <v>1.38</v>
@@ -20128,7 +20155,7 @@
         <v>0.25</v>
       </c>
       <c r="AP92">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ92">
         <v>0.63</v>
@@ -20256,7 +20283,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -20334,7 +20361,7 @@
         <v>1.2</v>
       </c>
       <c r="AP93">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ93">
         <v>0.78</v>
@@ -20540,7 +20567,7 @@
         <v>0</v>
       </c>
       <c r="AP94">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ94">
         <v>0.11</v>
@@ -20749,7 +20776,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ95">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR95">
         <v>1.86</v>
@@ -20874,7 +20901,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -20955,7 +20982,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ96">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR96">
         <v>1.68</v>
@@ -21364,7 +21391,7 @@
         <v>2</v>
       </c>
       <c r="AP98">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ98">
         <v>1.78</v>
@@ -21492,7 +21519,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -21570,7 +21597,7 @@
         <v>2</v>
       </c>
       <c r="AP99">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ99">
         <v>1.75</v>
@@ -21779,7 +21806,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ100">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR100">
         <v>1.65</v>
@@ -21904,7 +21931,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22110,7 +22137,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22316,7 +22343,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22397,7 +22424,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ103">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR103">
         <v>1.49</v>
@@ -22728,7 +22755,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -22809,7 +22836,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ105">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR105">
         <v>1.47</v>
@@ -22934,7 +22961,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -23140,7 +23167,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23427,7 +23454,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ108">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR108">
         <v>1.45</v>
@@ -23552,7 +23579,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -23630,7 +23657,7 @@
         <v>1.67</v>
       </c>
       <c r="AP109">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ109">
         <v>1.78</v>
@@ -23758,7 +23785,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -23836,7 +23863,7 @@
         <v>0.83</v>
       </c>
       <c r="AP110">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ110">
         <v>0.5600000000000001</v>
@@ -23964,7 +23991,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24042,10 +24069,10 @@
         <v>1.67</v>
       </c>
       <c r="AP111">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ111">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR111">
         <v>1.13</v>
@@ -24170,7 +24197,7 @@
         <v>96</v>
       </c>
       <c r="P112" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="Q112">
         <v>3.4</v>
@@ -24376,7 +24403,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24454,7 +24481,7 @@
         <v>0.2</v>
       </c>
       <c r="AP113">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ113">
         <v>0.63</v>
@@ -24582,7 +24609,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -24660,7 +24687,7 @@
         <v>1</v>
       </c>
       <c r="AP114">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ114">
         <v>0.78</v>
@@ -24788,7 +24815,7 @@
         <v>169</v>
       </c>
       <c r="P115" t="s">
-        <v>245</v>
+        <v>199</v>
       </c>
       <c r="Q115">
         <v>1.62</v>
@@ -24866,10 +24893,10 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ115">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR115">
         <v>2.31</v>
@@ -24994,7 +25021,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25075,7 +25102,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ116">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR116">
         <v>1.64</v>
@@ -25200,7 +25227,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25406,7 +25433,7 @@
         <v>171</v>
       </c>
       <c r="P118" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25487,7 +25514,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ118">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR118">
         <v>1.77</v>
@@ -25612,7 +25639,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -25693,7 +25720,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ119">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR119">
         <v>1.52</v>
@@ -25818,7 +25845,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26024,7 +26051,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26230,7 +26257,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26436,7 +26463,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="Q123">
         <v>1.91</v>
@@ -26642,7 +26669,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26848,7 +26875,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -26926,7 +26953,7 @@
         <v>1</v>
       </c>
       <c r="AP125">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ125">
         <v>1.5</v>
@@ -27054,7 +27081,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27135,7 +27162,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ126">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR126">
         <v>1.74</v>
@@ -27260,7 +27287,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27466,7 +27493,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27544,10 +27571,10 @@
         <v>1.86</v>
       </c>
       <c r="AP128">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ128">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR128">
         <v>2.15</v>
@@ -27672,7 +27699,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27750,7 +27777,7 @@
         <v>0.33</v>
       </c>
       <c r="AP129">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ129">
         <v>0.63</v>
@@ -27878,7 +27905,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -27956,10 +27983,10 @@
         <v>0.86</v>
       </c>
       <c r="AP130">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ130">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR130">
         <v>1.98</v>
@@ -28084,7 +28111,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28162,7 +28189,7 @@
         <v>1.83</v>
       </c>
       <c r="AP131">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ131">
         <v>1.75</v>
@@ -28290,7 +28317,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28371,7 +28398,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ132">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR132">
         <v>1.76</v>
@@ -28496,7 +28523,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28780,10 +28807,10 @@
         <v>1.14</v>
       </c>
       <c r="AP134">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ134">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR134">
         <v>2.13</v>
@@ -29114,7 +29141,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29195,7 +29222,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ136">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR136">
         <v>1.28</v>
@@ -29320,7 +29347,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -29607,7 +29634,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ138">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR138">
         <v>1.83</v>
@@ -29810,7 +29837,7 @@
         <v>0.63</v>
       </c>
       <c r="AP139">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ139">
         <v>0.5600000000000001</v>
@@ -29938,7 +29965,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="Q140">
         <v>1.83</v>
@@ -30350,7 +30377,7 @@
         <v>96</v>
       </c>
       <c r="P142" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30556,7 +30583,7 @@
         <v>96</v>
       </c>
       <c r="P143" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -30762,7 +30789,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -30968,7 +30995,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31174,7 +31201,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31252,10 +31279,10 @@
         <v>0.71</v>
       </c>
       <c r="AP146">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ146">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR146">
         <v>1.19</v>
@@ -31458,10 +31485,10 @@
         <v>1</v>
       </c>
       <c r="AP147">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ147">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR147">
         <v>1.77</v>
@@ -31667,7 +31694,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ148">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR148">
         <v>1.3</v>
@@ -31870,7 +31897,7 @@
         <v>2</v>
       </c>
       <c r="AP149">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ149">
         <v>1.75</v>
@@ -32079,7 +32106,7 @@
         <v>1</v>
       </c>
       <c r="AQ150">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR150">
         <v>1.25</v>
@@ -32204,7 +32231,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32282,10 +32309,10 @@
         <v>1.63</v>
       </c>
       <c r="AP151">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ151">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR151">
         <v>1.96</v>
@@ -32488,10 +32515,10 @@
         <v>0.57</v>
       </c>
       <c r="AP152">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ152">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR152">
         <v>2.19</v>
@@ -32616,7 +32643,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -32822,7 +32849,7 @@
         <v>96</v>
       </c>
       <c r="P154" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -32979,6 +33006,1448 @@
       </c>
       <c r="BP154">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="155" spans="1:68">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>7491970</v>
+      </c>
+      <c r="C155" t="s">
+        <v>68</v>
+      </c>
+      <c r="D155" t="s">
+        <v>69</v>
+      </c>
+      <c r="E155" s="2">
+        <v>45674.6875</v>
+      </c>
+      <c r="F155">
+        <v>18</v>
+      </c>
+      <c r="G155" t="s">
+        <v>82</v>
+      </c>
+      <c r="H155" t="s">
+        <v>76</v>
+      </c>
+      <c r="I155">
+        <v>1</v>
+      </c>
+      <c r="J155">
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <v>1</v>
+      </c>
+      <c r="L155">
+        <v>2</v>
+      </c>
+      <c r="M155">
+        <v>0</v>
+      </c>
+      <c r="N155">
+        <v>2</v>
+      </c>
+      <c r="O155" t="s">
+        <v>198</v>
+      </c>
+      <c r="P155" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q155">
+        <v>2.88</v>
+      </c>
+      <c r="R155">
+        <v>2.4</v>
+      </c>
+      <c r="S155">
+        <v>3.1</v>
+      </c>
+      <c r="T155">
+        <v>1.29</v>
+      </c>
+      <c r="U155">
+        <v>3.5</v>
+      </c>
+      <c r="V155">
+        <v>2.25</v>
+      </c>
+      <c r="W155">
+        <v>1.57</v>
+      </c>
+      <c r="X155">
+        <v>5.5</v>
+      </c>
+      <c r="Y155">
+        <v>1.14</v>
+      </c>
+      <c r="Z155">
+        <v>2.65</v>
+      </c>
+      <c r="AA155">
+        <v>3.75</v>
+      </c>
+      <c r="AB155">
+        <v>2.41</v>
+      </c>
+      <c r="AC155">
+        <v>1.01</v>
+      </c>
+      <c r="AD155">
+        <v>23</v>
+      </c>
+      <c r="AE155">
+        <v>1.15</v>
+      </c>
+      <c r="AF155">
+        <v>5.5</v>
+      </c>
+      <c r="AG155">
+        <v>1.47</v>
+      </c>
+      <c r="AH155">
+        <v>2.57</v>
+      </c>
+      <c r="AI155">
+        <v>1.44</v>
+      </c>
+      <c r="AJ155">
+        <v>2.63</v>
+      </c>
+      <c r="AK155">
+        <v>1.53</v>
+      </c>
+      <c r="AL155">
+        <v>1.26</v>
+      </c>
+      <c r="AM155">
+        <v>1.49</v>
+      </c>
+      <c r="AN155">
+        <v>2.13</v>
+      </c>
+      <c r="AO155">
+        <v>0.63</v>
+      </c>
+      <c r="AP155">
+        <v>2.22</v>
+      </c>
+      <c r="AQ155">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR155">
+        <v>1.87</v>
+      </c>
+      <c r="AS155">
+        <v>1.22</v>
+      </c>
+      <c r="AT155">
+        <v>3.09</v>
+      </c>
+      <c r="AU155">
+        <v>6</v>
+      </c>
+      <c r="AV155">
+        <v>4</v>
+      </c>
+      <c r="AW155">
+        <v>8</v>
+      </c>
+      <c r="AX155">
+        <v>9</v>
+      </c>
+      <c r="AY155">
+        <v>15</v>
+      </c>
+      <c r="AZ155">
+        <v>14</v>
+      </c>
+      <c r="BA155">
+        <v>5</v>
+      </c>
+      <c r="BB155">
+        <v>7</v>
+      </c>
+      <c r="BC155">
+        <v>12</v>
+      </c>
+      <c r="BD155">
+        <v>1.98</v>
+      </c>
+      <c r="BE155">
+        <v>6.5</v>
+      </c>
+      <c r="BF155">
+        <v>1.98</v>
+      </c>
+      <c r="BG155">
+        <v>1.26</v>
+      </c>
+      <c r="BH155">
+        <v>3.4</v>
+      </c>
+      <c r="BI155">
+        <v>1.46</v>
+      </c>
+      <c r="BJ155">
+        <v>2.48</v>
+      </c>
+      <c r="BK155">
+        <v>1.75</v>
+      </c>
+      <c r="BL155">
+        <v>1.95</v>
+      </c>
+      <c r="BM155">
+        <v>2.17</v>
+      </c>
+      <c r="BN155">
+        <v>1.6</v>
+      </c>
+      <c r="BO155">
+        <v>2.8</v>
+      </c>
+      <c r="BP155">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="156" spans="1:68">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>7491975</v>
+      </c>
+      <c r="C156" t="s">
+        <v>68</v>
+      </c>
+      <c r="D156" t="s">
+        <v>69</v>
+      </c>
+      <c r="E156" s="2">
+        <v>45675.47916666666</v>
+      </c>
+      <c r="F156">
+        <v>18</v>
+      </c>
+      <c r="G156" t="s">
+        <v>81</v>
+      </c>
+      <c r="H156" t="s">
+        <v>72</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>2</v>
+      </c>
+      <c r="K156">
+        <v>2</v>
+      </c>
+      <c r="L156">
+        <v>1</v>
+      </c>
+      <c r="M156">
+        <v>3</v>
+      </c>
+      <c r="N156">
+        <v>4</v>
+      </c>
+      <c r="O156" t="s">
+        <v>199</v>
+      </c>
+      <c r="P156" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q156">
+        <v>3.4</v>
+      </c>
+      <c r="R156">
+        <v>2.3</v>
+      </c>
+      <c r="S156">
+        <v>2.75</v>
+      </c>
+      <c r="T156">
+        <v>1.3</v>
+      </c>
+      <c r="U156">
+        <v>3.4</v>
+      </c>
+      <c r="V156">
+        <v>2.5</v>
+      </c>
+      <c r="W156">
+        <v>1.5</v>
+      </c>
+      <c r="X156">
+        <v>6</v>
+      </c>
+      <c r="Y156">
+        <v>1.13</v>
+      </c>
+      <c r="Z156">
+        <v>2.85</v>
+      </c>
+      <c r="AA156">
+        <v>3.42</v>
+      </c>
+      <c r="AB156">
+        <v>2.18</v>
+      </c>
+      <c r="AC156">
+        <v>1.03</v>
+      </c>
+      <c r="AD156">
+        <v>15</v>
+      </c>
+      <c r="AE156">
+        <v>1.19</v>
+      </c>
+      <c r="AF156">
+        <v>4.75</v>
+      </c>
+      <c r="AG156">
+        <v>1.6</v>
+      </c>
+      <c r="AH156">
+        <v>2.25</v>
+      </c>
+      <c r="AI156">
+        <v>1.53</v>
+      </c>
+      <c r="AJ156">
+        <v>2.38</v>
+      </c>
+      <c r="AK156">
+        <v>1.62</v>
+      </c>
+      <c r="AL156">
+        <v>1.27</v>
+      </c>
+      <c r="AM156">
+        <v>1.39</v>
+      </c>
+      <c r="AN156">
+        <v>1</v>
+      </c>
+      <c r="AO156">
+        <v>0.5</v>
+      </c>
+      <c r="AP156">
+        <v>0.9</v>
+      </c>
+      <c r="AQ156">
+        <v>0.78</v>
+      </c>
+      <c r="AR156">
+        <v>1.22</v>
+      </c>
+      <c r="AS156">
+        <v>1.06</v>
+      </c>
+      <c r="AT156">
+        <v>2.28</v>
+      </c>
+      <c r="AU156">
+        <v>4</v>
+      </c>
+      <c r="AV156">
+        <v>7</v>
+      </c>
+      <c r="AW156">
+        <v>9</v>
+      </c>
+      <c r="AX156">
+        <v>5</v>
+      </c>
+      <c r="AY156">
+        <v>15</v>
+      </c>
+      <c r="AZ156">
+        <v>14</v>
+      </c>
+      <c r="BA156">
+        <v>4</v>
+      </c>
+      <c r="BB156">
+        <v>3</v>
+      </c>
+      <c r="BC156">
+        <v>7</v>
+      </c>
+      <c r="BD156">
+        <v>1.98</v>
+      </c>
+      <c r="BE156">
+        <v>6.4</v>
+      </c>
+      <c r="BF156">
+        <v>2</v>
+      </c>
+      <c r="BG156">
+        <v>1.25</v>
+      </c>
+      <c r="BH156">
+        <v>3.4</v>
+      </c>
+      <c r="BI156">
+        <v>1.46</v>
+      </c>
+      <c r="BJ156">
+        <v>2.5</v>
+      </c>
+      <c r="BK156">
+        <v>1.73</v>
+      </c>
+      <c r="BL156">
+        <v>1.97</v>
+      </c>
+      <c r="BM156">
+        <v>2.15</v>
+      </c>
+      <c r="BN156">
+        <v>1.61</v>
+      </c>
+      <c r="BO156">
+        <v>2.7</v>
+      </c>
+      <c r="BP156">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="157" spans="1:68">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157">
+        <v>7491974</v>
+      </c>
+      <c r="C157" t="s">
+        <v>68</v>
+      </c>
+      <c r="D157" t="s">
+        <v>69</v>
+      </c>
+      <c r="E157" s="2">
+        <v>45675.47916666666</v>
+      </c>
+      <c r="F157">
+        <v>18</v>
+      </c>
+      <c r="G157" t="s">
+        <v>83</v>
+      </c>
+      <c r="H157" t="s">
+        <v>71</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+      <c r="J157">
+        <v>3</v>
+      </c>
+      <c r="K157">
+        <v>3</v>
+      </c>
+      <c r="L157">
+        <v>3</v>
+      </c>
+      <c r="M157">
+        <v>3</v>
+      </c>
+      <c r="N157">
+        <v>6</v>
+      </c>
+      <c r="O157" t="s">
+        <v>200</v>
+      </c>
+      <c r="P157" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q157">
+        <v>4.33</v>
+      </c>
+      <c r="R157">
+        <v>2.4</v>
+      </c>
+      <c r="S157">
+        <v>2.25</v>
+      </c>
+      <c r="T157">
+        <v>1.29</v>
+      </c>
+      <c r="U157">
+        <v>3.5</v>
+      </c>
+      <c r="V157">
+        <v>2.25</v>
+      </c>
+      <c r="W157">
+        <v>1.57</v>
+      </c>
+      <c r="X157">
+        <v>5.5</v>
+      </c>
+      <c r="Y157">
+        <v>1.14</v>
+      </c>
+      <c r="Z157">
+        <v>3.99</v>
+      </c>
+      <c r="AA157">
+        <v>3.73</v>
+      </c>
+      <c r="AB157">
+        <v>1.64</v>
+      </c>
+      <c r="AC157">
+        <v>1.02</v>
+      </c>
+      <c r="AD157">
+        <v>21</v>
+      </c>
+      <c r="AE157">
+        <v>1.18</v>
+      </c>
+      <c r="AF157">
+        <v>5</v>
+      </c>
+      <c r="AG157">
+        <v>1.65</v>
+      </c>
+      <c r="AH157">
+        <v>2.16</v>
+      </c>
+      <c r="AI157">
+        <v>1.57</v>
+      </c>
+      <c r="AJ157">
+        <v>2.25</v>
+      </c>
+      <c r="AK157">
+        <v>1.98</v>
+      </c>
+      <c r="AL157">
+        <v>1.23</v>
+      </c>
+      <c r="AM157">
+        <v>1.24</v>
+      </c>
+      <c r="AN157">
+        <v>1</v>
+      </c>
+      <c r="AO157">
+        <v>1.44</v>
+      </c>
+      <c r="AP157">
+        <v>1</v>
+      </c>
+      <c r="AQ157">
+        <v>1.4</v>
+      </c>
+      <c r="AR157">
+        <v>1.22</v>
+      </c>
+      <c r="AS157">
+        <v>1.1</v>
+      </c>
+      <c r="AT157">
+        <v>2.32</v>
+      </c>
+      <c r="AU157">
+        <v>4</v>
+      </c>
+      <c r="AV157">
+        <v>4</v>
+      </c>
+      <c r="AW157">
+        <v>6</v>
+      </c>
+      <c r="AX157">
+        <v>7</v>
+      </c>
+      <c r="AY157">
+        <v>15</v>
+      </c>
+      <c r="AZ157">
+        <v>12</v>
+      </c>
+      <c r="BA157">
+        <v>6</v>
+      </c>
+      <c r="BB157">
+        <v>3</v>
+      </c>
+      <c r="BC157">
+        <v>9</v>
+      </c>
+      <c r="BD157">
+        <v>2.55</v>
+      </c>
+      <c r="BE157">
+        <v>6.5</v>
+      </c>
+      <c r="BF157">
+        <v>1.61</v>
+      </c>
+      <c r="BG157">
+        <v>1.29</v>
+      </c>
+      <c r="BH157">
+        <v>3.2</v>
+      </c>
+      <c r="BI157">
+        <v>1.5</v>
+      </c>
+      <c r="BJ157">
+        <v>2.38</v>
+      </c>
+      <c r="BK157">
+        <v>1.81</v>
+      </c>
+      <c r="BL157">
+        <v>1.88</v>
+      </c>
+      <c r="BM157">
+        <v>2.28</v>
+      </c>
+      <c r="BN157">
+        <v>1.54</v>
+      </c>
+      <c r="BO157">
+        <v>2.9</v>
+      </c>
+      <c r="BP157">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="158" spans="1:68">
+      <c r="A158" s="1">
+        <v>157</v>
+      </c>
+      <c r="B158">
+        <v>7491971</v>
+      </c>
+      <c r="C158" t="s">
+        <v>68</v>
+      </c>
+      <c r="D158" t="s">
+        <v>69</v>
+      </c>
+      <c r="E158" s="2">
+        <v>45675.47916666666</v>
+      </c>
+      <c r="F158">
+        <v>18</v>
+      </c>
+      <c r="G158" t="s">
+        <v>86</v>
+      </c>
+      <c r="H158" t="s">
+        <v>78</v>
+      </c>
+      <c r="I158">
+        <v>0</v>
+      </c>
+      <c r="J158">
+        <v>1</v>
+      </c>
+      <c r="K158">
+        <v>1</v>
+      </c>
+      <c r="L158">
+        <v>0</v>
+      </c>
+      <c r="M158">
+        <v>2</v>
+      </c>
+      <c r="N158">
+        <v>2</v>
+      </c>
+      <c r="O158" t="s">
+        <v>96</v>
+      </c>
+      <c r="P158" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q158">
+        <v>3.2</v>
+      </c>
+      <c r="R158">
+        <v>2.1</v>
+      </c>
+      <c r="S158">
+        <v>3.25</v>
+      </c>
+      <c r="T158">
+        <v>1.4</v>
+      </c>
+      <c r="U158">
+        <v>2.75</v>
+      </c>
+      <c r="V158">
+        <v>2.75</v>
+      </c>
+      <c r="W158">
+        <v>1.4</v>
+      </c>
+      <c r="X158">
+        <v>8</v>
+      </c>
+      <c r="Y158">
+        <v>1.08</v>
+      </c>
+      <c r="Z158">
+        <v>2.47</v>
+      </c>
+      <c r="AA158">
+        <v>3.17</v>
+      </c>
+      <c r="AB158">
+        <v>2.62</v>
+      </c>
+      <c r="AC158">
+        <v>1.05</v>
+      </c>
+      <c r="AD158">
+        <v>11</v>
+      </c>
+      <c r="AE158">
+        <v>1.32</v>
+      </c>
+      <c r="AF158">
+        <v>3.4</v>
+      </c>
+      <c r="AG158">
+        <v>1.97</v>
+      </c>
+      <c r="AH158">
+        <v>1.89</v>
+      </c>
+      <c r="AI158">
+        <v>1.75</v>
+      </c>
+      <c r="AJ158">
+        <v>2</v>
+      </c>
+      <c r="AK158">
+        <v>1.46</v>
+      </c>
+      <c r="AL158">
+        <v>1.31</v>
+      </c>
+      <c r="AM158">
+        <v>1.49</v>
+      </c>
+      <c r="AN158">
+        <v>0.88</v>
+      </c>
+      <c r="AO158">
+        <v>1</v>
+      </c>
+      <c r="AP158">
+        <v>0.78</v>
+      </c>
+      <c r="AQ158">
+        <v>1.2</v>
+      </c>
+      <c r="AR158">
+        <v>1.38</v>
+      </c>
+      <c r="AS158">
+        <v>1.17</v>
+      </c>
+      <c r="AT158">
+        <v>2.55</v>
+      </c>
+      <c r="AU158">
+        <v>3</v>
+      </c>
+      <c r="AV158">
+        <v>4</v>
+      </c>
+      <c r="AW158">
+        <v>7</v>
+      </c>
+      <c r="AX158">
+        <v>3</v>
+      </c>
+      <c r="AY158">
+        <v>10</v>
+      </c>
+      <c r="AZ158">
+        <v>9</v>
+      </c>
+      <c r="BA158">
+        <v>4</v>
+      </c>
+      <c r="BB158">
+        <v>4</v>
+      </c>
+      <c r="BC158">
+        <v>8</v>
+      </c>
+      <c r="BD158">
+        <v>1.79</v>
+      </c>
+      <c r="BE158">
+        <v>6.4</v>
+      </c>
+      <c r="BF158">
+        <v>2.23</v>
+      </c>
+      <c r="BG158">
+        <v>1.35</v>
+      </c>
+      <c r="BH158">
+        <v>2.88</v>
+      </c>
+      <c r="BI158">
+        <v>1.61</v>
+      </c>
+      <c r="BJ158">
+        <v>2.15</v>
+      </c>
+      <c r="BK158">
+        <v>1.98</v>
+      </c>
+      <c r="BL158">
+        <v>1.72</v>
+      </c>
+      <c r="BM158">
+        <v>2.55</v>
+      </c>
+      <c r="BN158">
+        <v>1.44</v>
+      </c>
+      <c r="BO158">
+        <v>3.3</v>
+      </c>
+      <c r="BP158">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="159" spans="1:68">
+      <c r="A159" s="1">
+        <v>158</v>
+      </c>
+      <c r="B159">
+        <v>7491968</v>
+      </c>
+      <c r="C159" t="s">
+        <v>68</v>
+      </c>
+      <c r="D159" t="s">
+        <v>69</v>
+      </c>
+      <c r="E159" s="2">
+        <v>45675.47916666666</v>
+      </c>
+      <c r="F159">
+        <v>18</v>
+      </c>
+      <c r="G159" t="s">
+        <v>80</v>
+      </c>
+      <c r="H159" t="s">
+        <v>73</v>
+      </c>
+      <c r="I159">
+        <v>3</v>
+      </c>
+      <c r="J159">
+        <v>0</v>
+      </c>
+      <c r="K159">
+        <v>3</v>
+      </c>
+      <c r="L159">
+        <v>4</v>
+      </c>
+      <c r="M159">
+        <v>0</v>
+      </c>
+      <c r="N159">
+        <v>4</v>
+      </c>
+      <c r="O159" t="s">
+        <v>201</v>
+      </c>
+      <c r="P159" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q159">
+        <v>2.2</v>
+      </c>
+      <c r="R159">
+        <v>2.4</v>
+      </c>
+      <c r="S159">
+        <v>4.5</v>
+      </c>
+      <c r="T159">
+        <v>1.29</v>
+      </c>
+      <c r="U159">
+        <v>3.5</v>
+      </c>
+      <c r="V159">
+        <v>2.25</v>
+      </c>
+      <c r="W159">
+        <v>1.57</v>
+      </c>
+      <c r="X159">
+        <v>5.5</v>
+      </c>
+      <c r="Y159">
+        <v>1.14</v>
+      </c>
+      <c r="Z159">
+        <v>1.67</v>
+      </c>
+      <c r="AA159">
+        <v>3.84</v>
+      </c>
+      <c r="AB159">
+        <v>4.11</v>
+      </c>
+      <c r="AC159">
+        <v>1.02</v>
+      </c>
+      <c r="AD159">
+        <v>19</v>
+      </c>
+      <c r="AE159">
+        <v>1.18</v>
+      </c>
+      <c r="AF159">
+        <v>5</v>
+      </c>
+      <c r="AG159">
+        <v>1.5</v>
+      </c>
+      <c r="AH159">
+        <v>2.48</v>
+      </c>
+      <c r="AI159">
+        <v>1.62</v>
+      </c>
+      <c r="AJ159">
+        <v>2.2</v>
+      </c>
+      <c r="AK159">
+        <v>1.25</v>
+      </c>
+      <c r="AL159">
+        <v>1.25</v>
+      </c>
+      <c r="AM159">
+        <v>1.93</v>
+      </c>
+      <c r="AN159">
+        <v>1.89</v>
+      </c>
+      <c r="AO159">
+        <v>0.89</v>
+      </c>
+      <c r="AP159">
+        <v>2</v>
+      </c>
+      <c r="AQ159">
+        <v>0.8</v>
+      </c>
+      <c r="AR159">
+        <v>1.95</v>
+      </c>
+      <c r="AS159">
+        <v>1.24</v>
+      </c>
+      <c r="AT159">
+        <v>3.19</v>
+      </c>
+      <c r="AU159">
+        <v>8</v>
+      </c>
+      <c r="AV159">
+        <v>0</v>
+      </c>
+      <c r="AW159">
+        <v>5</v>
+      </c>
+      <c r="AX159">
+        <v>5</v>
+      </c>
+      <c r="AY159">
+        <v>15</v>
+      </c>
+      <c r="AZ159">
+        <v>7</v>
+      </c>
+      <c r="BA159">
+        <v>4</v>
+      </c>
+      <c r="BB159">
+        <v>1</v>
+      </c>
+      <c r="BC159">
+        <v>5</v>
+      </c>
+      <c r="BD159">
+        <v>1.44</v>
+      </c>
+      <c r="BE159">
+        <v>7</v>
+      </c>
+      <c r="BF159">
+        <v>3.15</v>
+      </c>
+      <c r="BG159">
+        <v>1.3</v>
+      </c>
+      <c r="BH159">
+        <v>3.05</v>
+      </c>
+      <c r="BI159">
+        <v>1.54</v>
+      </c>
+      <c r="BJ159">
+        <v>2.3</v>
+      </c>
+      <c r="BK159">
+        <v>1.89</v>
+      </c>
+      <c r="BL159">
+        <v>1.8</v>
+      </c>
+      <c r="BM159">
+        <v>2.4</v>
+      </c>
+      <c r="BN159">
+        <v>1.5</v>
+      </c>
+      <c r="BO159">
+        <v>3.15</v>
+      </c>
+      <c r="BP159">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="160" spans="1:68">
+      <c r="A160" s="1">
+        <v>159</v>
+      </c>
+      <c r="B160">
+        <v>7491969</v>
+      </c>
+      <c r="C160" t="s">
+        <v>68</v>
+      </c>
+      <c r="D160" t="s">
+        <v>69</v>
+      </c>
+      <c r="E160" s="2">
+        <v>45675.47916666666</v>
+      </c>
+      <c r="F160">
+        <v>18</v>
+      </c>
+      <c r="G160" t="s">
+        <v>87</v>
+      </c>
+      <c r="H160" t="s">
+        <v>77</v>
+      </c>
+      <c r="I160">
+        <v>2</v>
+      </c>
+      <c r="J160">
+        <v>1</v>
+      </c>
+      <c r="K160">
+        <v>3</v>
+      </c>
+      <c r="L160">
+        <v>3</v>
+      </c>
+      <c r="M160">
+        <v>2</v>
+      </c>
+      <c r="N160">
+        <v>5</v>
+      </c>
+      <c r="O160" t="s">
+        <v>202</v>
+      </c>
+      <c r="P160" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q160">
+        <v>1.53</v>
+      </c>
+      <c r="R160">
+        <v>3.1</v>
+      </c>
+      <c r="S160">
+        <v>9</v>
+      </c>
+      <c r="T160">
+        <v>1.18</v>
+      </c>
+      <c r="U160">
+        <v>4.5</v>
+      </c>
+      <c r="V160">
+        <v>1.83</v>
+      </c>
+      <c r="W160">
+        <v>1.83</v>
+      </c>
+      <c r="X160">
+        <v>3.75</v>
+      </c>
+      <c r="Y160">
+        <v>1.25</v>
+      </c>
+      <c r="Z160">
+        <v>1.17</v>
+      </c>
+      <c r="AA160">
+        <v>6.28</v>
+      </c>
+      <c r="AB160">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="AC160">
+        <v>1</v>
+      </c>
+      <c r="AD160">
+        <v>23</v>
+      </c>
+      <c r="AE160">
+        <v>1.08</v>
+      </c>
+      <c r="AF160">
+        <v>8</v>
+      </c>
+      <c r="AG160">
+        <v>1.28</v>
+      </c>
+      <c r="AH160">
+        <v>3.47</v>
+      </c>
+      <c r="AI160">
+        <v>1.8</v>
+      </c>
+      <c r="AJ160">
+        <v>1.95</v>
+      </c>
+      <c r="AK160">
+        <v>1.03</v>
+      </c>
+      <c r="AL160">
+        <v>1.09</v>
+      </c>
+      <c r="AM160">
+        <v>4.6</v>
+      </c>
+      <c r="AN160">
+        <v>2.75</v>
+      </c>
+      <c r="AO160">
+        <v>2</v>
+      </c>
+      <c r="AP160">
+        <v>2.78</v>
+      </c>
+      <c r="AQ160">
+        <v>1.78</v>
+      </c>
+      <c r="AR160">
+        <v>2.29</v>
+      </c>
+      <c r="AS160">
+        <v>1.39</v>
+      </c>
+      <c r="AT160">
+        <v>3.68</v>
+      </c>
+      <c r="AU160">
+        <v>11</v>
+      </c>
+      <c r="AV160">
+        <v>4</v>
+      </c>
+      <c r="AW160">
+        <v>15</v>
+      </c>
+      <c r="AX160">
+        <v>4</v>
+      </c>
+      <c r="AY160">
+        <v>27</v>
+      </c>
+      <c r="AZ160">
+        <v>9</v>
+      </c>
+      <c r="BA160">
+        <v>6</v>
+      </c>
+      <c r="BB160">
+        <v>2</v>
+      </c>
+      <c r="BC160">
+        <v>8</v>
+      </c>
+      <c r="BD160">
+        <v>1.09</v>
+      </c>
+      <c r="BE160">
+        <v>11</v>
+      </c>
+      <c r="BF160">
+        <v>7</v>
+      </c>
+      <c r="BG160">
+        <v>1.27</v>
+      </c>
+      <c r="BH160">
+        <v>3.3</v>
+      </c>
+      <c r="BI160">
+        <v>1.47</v>
+      </c>
+      <c r="BJ160">
+        <v>2.48</v>
+      </c>
+      <c r="BK160">
+        <v>1.74</v>
+      </c>
+      <c r="BL160">
+        <v>1.96</v>
+      </c>
+      <c r="BM160">
+        <v>2.15</v>
+      </c>
+      <c r="BN160">
+        <v>1.61</v>
+      </c>
+      <c r="BO160">
+        <v>2.7</v>
+      </c>
+      <c r="BP160">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:68">
+      <c r="A161" s="1">
+        <v>160</v>
+      </c>
+      <c r="B161">
+        <v>7491967</v>
+      </c>
+      <c r="C161" t="s">
+        <v>68</v>
+      </c>
+      <c r="D161" t="s">
+        <v>69</v>
+      </c>
+      <c r="E161" s="2">
+        <v>45675.60416666666</v>
+      </c>
+      <c r="F161">
+        <v>18</v>
+      </c>
+      <c r="G161" t="s">
+        <v>85</v>
+      </c>
+      <c r="H161" t="s">
+        <v>70</v>
+      </c>
+      <c r="I161">
+        <v>1</v>
+      </c>
+      <c r="J161">
+        <v>0</v>
+      </c>
+      <c r="K161">
+        <v>1</v>
+      </c>
+      <c r="L161">
+        <v>3</v>
+      </c>
+      <c r="M161">
+        <v>1</v>
+      </c>
+      <c r="N161">
+        <v>4</v>
+      </c>
+      <c r="O161" t="s">
+        <v>203</v>
+      </c>
+      <c r="P161" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q161">
+        <v>1.73</v>
+      </c>
+      <c r="R161">
+        <v>2.75</v>
+      </c>
+      <c r="S161">
+        <v>7</v>
+      </c>
+      <c r="T161">
+        <v>1.22</v>
+      </c>
+      <c r="U161">
+        <v>4</v>
+      </c>
+      <c r="V161">
+        <v>2</v>
+      </c>
+      <c r="W161">
+        <v>1.73</v>
+      </c>
+      <c r="X161">
+        <v>4.33</v>
+      </c>
+      <c r="Y161">
+        <v>1.2</v>
+      </c>
+      <c r="Z161">
+        <v>1.3</v>
+      </c>
+      <c r="AA161">
+        <v>5.75</v>
+      </c>
+      <c r="AB161">
+        <v>10</v>
+      </c>
+      <c r="AC161">
+        <v>1.01</v>
+      </c>
+      <c r="AD161">
+        <v>17.5</v>
+      </c>
+      <c r="AE161">
+        <v>1.12</v>
+      </c>
+      <c r="AF161">
+        <v>6.5</v>
+      </c>
+      <c r="AG161">
+        <v>1.36</v>
+      </c>
+      <c r="AH161">
+        <v>2.99</v>
+      </c>
+      <c r="AI161">
+        <v>1.7</v>
+      </c>
+      <c r="AJ161">
+        <v>2.05</v>
+      </c>
+      <c r="AK161">
+        <v>1.07</v>
+      </c>
+      <c r="AL161">
+        <v>1.13</v>
+      </c>
+      <c r="AM161">
+        <v>3.4</v>
+      </c>
+      <c r="AN161">
+        <v>2.22</v>
+      </c>
+      <c r="AO161">
+        <v>1</v>
+      </c>
+      <c r="AP161">
+        <v>2.3</v>
+      </c>
+      <c r="AQ161">
+        <v>0.89</v>
+      </c>
+      <c r="AR161">
+        <v>2.2</v>
+      </c>
+      <c r="AS161">
+        <v>1.35</v>
+      </c>
+      <c r="AT161">
+        <v>3.55</v>
+      </c>
+      <c r="AU161">
+        <v>6</v>
+      </c>
+      <c r="AV161">
+        <v>5</v>
+      </c>
+      <c r="AW161">
+        <v>5</v>
+      </c>
+      <c r="AX161">
+        <v>3</v>
+      </c>
+      <c r="AY161">
+        <v>11</v>
+      </c>
+      <c r="AZ161">
+        <v>8</v>
+      </c>
+      <c r="BA161">
+        <v>7</v>
+      </c>
+      <c r="BB161">
+        <v>6</v>
+      </c>
+      <c r="BC161">
+        <v>13</v>
+      </c>
+      <c r="BD161">
+        <v>1.18</v>
+      </c>
+      <c r="BE161">
+        <v>9</v>
+      </c>
+      <c r="BF161">
+        <v>5.1</v>
+      </c>
+      <c r="BG161">
+        <v>1.26</v>
+      </c>
+      <c r="BH161">
+        <v>3.4</v>
+      </c>
+      <c r="BI161">
+        <v>1.47</v>
+      </c>
+      <c r="BJ161">
+        <v>2.48</v>
+      </c>
+      <c r="BK161">
+        <v>1.76</v>
+      </c>
+      <c r="BL161">
+        <v>1.94</v>
+      </c>
+      <c r="BM161">
+        <v>2.18</v>
+      </c>
+      <c r="BN161">
+        <v>1.58</v>
+      </c>
+      <c r="BO161">
+        <v>2.8</v>
+      </c>
+      <c r="BP161">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="304">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -628,6 +628,9 @@
     <t>['32', '62', '74']</t>
   </si>
   <si>
+    <t>['1', '24']</t>
+  </si>
+  <si>
     <t>['12', '38', '90+11']</t>
   </si>
   <si>
@@ -920,6 +923,9 @@
   </si>
   <si>
     <t>['24', '88']</t>
+  </si>
+  <si>
+    <t>['5', '45+1']</t>
   </si>
 </sst>
 </file>
@@ -1281,7 +1287,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP161"/>
+  <dimension ref="A1:BP163"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1537,7 +1543,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -1949,7 +1955,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2155,7 +2161,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2361,7 +2367,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2567,7 +2573,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2979,7 +2985,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3185,7 +3191,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3469,7 +3475,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ11">
         <v>1.2</v>
@@ -3597,7 +3603,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3678,7 +3684,7 @@
         <v>2</v>
       </c>
       <c r="AQ12">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3803,7 +3809,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -4009,7 +4015,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4215,7 +4221,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4499,7 +4505,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ16">
         <v>0.5600000000000001</v>
@@ -4627,7 +4633,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4914,7 +4920,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ18">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5245,7 +5251,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5657,7 +5663,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -6069,7 +6075,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6275,7 +6281,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6481,7 +6487,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -6687,7 +6693,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q27">
         <v>2.63</v>
@@ -6893,7 +6899,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7099,7 +7105,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7180,7 +7186,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ29">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR29">
         <v>1.7</v>
@@ -7305,7 +7311,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7511,7 +7517,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7589,7 +7595,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ31">
         <v>2.22</v>
@@ -7717,7 +7723,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7795,7 +7801,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ32">
         <v>0.78</v>
@@ -7923,7 +7929,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8335,7 +8341,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -8953,7 +8959,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9365,7 +9371,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9571,7 +9577,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9777,7 +9783,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -10064,7 +10070,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ43">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AR43">
         <v>1.14</v>
@@ -10189,7 +10195,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10395,7 +10401,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10601,7 +10607,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -11013,7 +11019,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11297,7 +11303,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ49">
         <v>0.8</v>
@@ -11425,7 +11431,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11503,7 +11509,7 @@
         <v>0.5</v>
       </c>
       <c r="AP50">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ50">
         <v>0.5600000000000001</v>
@@ -11631,7 +11637,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -11837,7 +11843,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11918,7 +11924,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ52">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR52">
         <v>1.52</v>
@@ -12249,7 +12255,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12455,7 +12461,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12661,7 +12667,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -12867,7 +12873,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -13279,7 +13285,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13360,7 +13366,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ59">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AR59">
         <v>1.71</v>
@@ -13485,7 +13491,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13691,7 +13697,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14103,7 +14109,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14309,7 +14315,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14515,7 +14521,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14721,7 +14727,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -15133,7 +15139,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15545,7 +15551,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15623,7 +15629,7 @@
         <v>2.33</v>
       </c>
       <c r="AP70">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ70">
         <v>2.25</v>
@@ -15751,7 +15757,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -15957,7 +15963,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16035,7 +16041,7 @@
         <v>1.5</v>
       </c>
       <c r="AP72">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ72">
         <v>1.78</v>
@@ -16781,7 +16787,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -16987,7 +16993,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -17480,7 +17486,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ79">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AR79">
         <v>1.14</v>
@@ -17892,7 +17898,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ81">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR81">
         <v>1.64</v>
@@ -18301,7 +18307,7 @@
         <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ83">
         <v>0.8</v>
@@ -18429,7 +18435,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18713,7 +18719,7 @@
         <v>0.5</v>
       </c>
       <c r="AP85">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ85">
         <v>0.25</v>
@@ -18841,7 +18847,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -19047,7 +19053,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19665,7 +19671,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19871,7 +19877,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -20158,7 +20164,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ92">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AR92">
         <v>1.83</v>
@@ -20283,7 +20289,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -20901,7 +20907,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21519,7 +21525,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -21600,7 +21606,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ99">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR99">
         <v>1.21</v>
@@ -21931,7 +21937,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22137,7 +22143,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22215,7 +22221,7 @@
         <v>1.8</v>
       </c>
       <c r="AP102">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ102">
         <v>2.25</v>
@@ -22343,7 +22349,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22755,7 +22761,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -22961,7 +22967,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -23039,7 +23045,7 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ106">
         <v>1.5</v>
@@ -23167,7 +23173,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23579,7 +23585,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -23785,7 +23791,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -23991,7 +23997,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24197,7 +24203,7 @@
         <v>96</v>
       </c>
       <c r="P112" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q112">
         <v>3.4</v>
@@ -24403,7 +24409,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24484,7 +24490,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ113">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AR113">
         <v>1.55</v>
@@ -24609,7 +24615,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -25021,7 +25027,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25227,7 +25233,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25308,7 +25314,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ117">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR117">
         <v>1.29</v>
@@ -25433,7 +25439,7 @@
         <v>171</v>
       </c>
       <c r="P118" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25639,7 +25645,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -25845,7 +25851,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -25923,7 +25929,7 @@
         <v>0</v>
       </c>
       <c r="AP120">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ120">
         <v>0.11</v>
@@ -26051,7 +26057,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26257,7 +26263,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26463,7 +26469,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q123">
         <v>1.91</v>
@@ -26669,7 +26675,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26875,7 +26881,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -27081,7 +27087,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27287,7 +27293,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27493,7 +27499,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27699,7 +27705,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27780,7 +27786,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ129">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AR129">
         <v>1.19</v>
@@ -27905,7 +27911,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -28111,7 +28117,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28192,7 +28198,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ131">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR131">
         <v>1.54</v>
@@ -28317,7 +28323,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28523,7 +28529,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28601,7 +28607,7 @@
         <v>0.71</v>
       </c>
       <c r="AP133">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ133">
         <v>0.5600000000000001</v>
@@ -29141,7 +29147,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29347,7 +29353,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -29965,7 +29971,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q140">
         <v>1.83</v>
@@ -30377,7 +30383,7 @@
         <v>96</v>
       </c>
       <c r="P142" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30583,7 +30589,7 @@
         <v>96</v>
       </c>
       <c r="P143" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -30789,7 +30795,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -30995,7 +31001,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31201,7 +31207,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31900,7 +31906,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ149">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR149">
         <v>2.17</v>
@@ -32231,7 +32237,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32643,7 +32649,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -32721,7 +32727,7 @@
         <v>0.75</v>
       </c>
       <c r="AP153">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ153">
         <v>0.78</v>
@@ -32849,7 +32855,7 @@
         <v>96</v>
       </c>
       <c r="P154" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -32927,10 +32933,10 @@
         <v>0.29</v>
       </c>
       <c r="AP154">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ154">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AR154">
         <v>1.41</v>
@@ -33261,7 +33267,7 @@
         <v>199</v>
       </c>
       <c r="P156" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q156">
         <v>3.4</v>
@@ -33467,7 +33473,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33673,7 +33679,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q158">
         <v>3.2</v>
@@ -34085,7 +34091,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q160">
         <v>1.53</v>
@@ -34291,7 +34297,7 @@
         <v>203</v>
       </c>
       <c r="P161" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q161">
         <v>1.73</v>
@@ -34448,6 +34454,418 @@
       </c>
       <c r="BP161">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="162" spans="1:68">
+      <c r="A162" s="1">
+        <v>161</v>
+      </c>
+      <c r="B162">
+        <v>7491973</v>
+      </c>
+      <c r="C162" t="s">
+        <v>68</v>
+      </c>
+      <c r="D162" t="s">
+        <v>69</v>
+      </c>
+      <c r="E162" s="2">
+        <v>45676.47916666666</v>
+      </c>
+      <c r="F162">
+        <v>18</v>
+      </c>
+      <c r="G162" t="s">
+        <v>79</v>
+      </c>
+      <c r="H162" t="s">
+        <v>75</v>
+      </c>
+      <c r="I162">
+        <v>2</v>
+      </c>
+      <c r="J162">
+        <v>1</v>
+      </c>
+      <c r="K162">
+        <v>3</v>
+      </c>
+      <c r="L162">
+        <v>2</v>
+      </c>
+      <c r="M162">
+        <v>1</v>
+      </c>
+      <c r="N162">
+        <v>3</v>
+      </c>
+      <c r="O162" t="s">
+        <v>204</v>
+      </c>
+      <c r="P162" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q162">
+        <v>3.25</v>
+      </c>
+      <c r="R162">
+        <v>2.05</v>
+      </c>
+      <c r="S162">
+        <v>3.5</v>
+      </c>
+      <c r="T162">
+        <v>1.44</v>
+      </c>
+      <c r="U162">
+        <v>2.63</v>
+      </c>
+      <c r="V162">
+        <v>3.25</v>
+      </c>
+      <c r="W162">
+        <v>1.33</v>
+      </c>
+      <c r="X162">
+        <v>9</v>
+      </c>
+      <c r="Y162">
+        <v>1.07</v>
+      </c>
+      <c r="Z162">
+        <v>2.6</v>
+      </c>
+      <c r="AA162">
+        <v>3.2</v>
+      </c>
+      <c r="AB162">
+        <v>2.87</v>
+      </c>
+      <c r="AC162">
+        <v>1.07</v>
+      </c>
+      <c r="AD162">
+        <v>9.5</v>
+      </c>
+      <c r="AE162">
+        <v>1.36</v>
+      </c>
+      <c r="AF162">
+        <v>3.2</v>
+      </c>
+      <c r="AG162">
+        <v>2.05</v>
+      </c>
+      <c r="AH162">
+        <v>1.72</v>
+      </c>
+      <c r="AI162">
+        <v>1.8</v>
+      </c>
+      <c r="AJ162">
+        <v>1.95</v>
+      </c>
+      <c r="AK162">
+        <v>1.43</v>
+      </c>
+      <c r="AL162">
+        <v>1.31</v>
+      </c>
+      <c r="AM162">
+        <v>1.51</v>
+      </c>
+      <c r="AN162">
+        <v>1.5</v>
+      </c>
+      <c r="AO162">
+        <v>1.75</v>
+      </c>
+      <c r="AP162">
+        <v>1.67</v>
+      </c>
+      <c r="AQ162">
+        <v>1.56</v>
+      </c>
+      <c r="AR162">
+        <v>1.42</v>
+      </c>
+      <c r="AS162">
+        <v>1.14</v>
+      </c>
+      <c r="AT162">
+        <v>2.56</v>
+      </c>
+      <c r="AU162">
+        <v>5</v>
+      </c>
+      <c r="AV162">
+        <v>2</v>
+      </c>
+      <c r="AW162">
+        <v>8</v>
+      </c>
+      <c r="AX162">
+        <v>8</v>
+      </c>
+      <c r="AY162">
+        <v>15</v>
+      </c>
+      <c r="AZ162">
+        <v>12</v>
+      </c>
+      <c r="BA162">
+        <v>2</v>
+      </c>
+      <c r="BB162">
+        <v>2</v>
+      </c>
+      <c r="BC162">
+        <v>4</v>
+      </c>
+      <c r="BD162">
+        <v>1.83</v>
+      </c>
+      <c r="BE162">
+        <v>6.5</v>
+      </c>
+      <c r="BF162">
+        <v>2.17</v>
+      </c>
+      <c r="BG162">
+        <v>1.27</v>
+      </c>
+      <c r="BH162">
+        <v>3.3</v>
+      </c>
+      <c r="BI162">
+        <v>1.48</v>
+      </c>
+      <c r="BJ162">
+        <v>2.45</v>
+      </c>
+      <c r="BK162">
+        <v>1.76</v>
+      </c>
+      <c r="BL162">
+        <v>1.94</v>
+      </c>
+      <c r="BM162">
+        <v>2.18</v>
+      </c>
+      <c r="BN162">
+        <v>1.58</v>
+      </c>
+      <c r="BO162">
+        <v>2.8</v>
+      </c>
+      <c r="BP162">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="163" spans="1:68">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="B163">
+        <v>7491972</v>
+      </c>
+      <c r="C163" t="s">
+        <v>68</v>
+      </c>
+      <c r="D163" t="s">
+        <v>69</v>
+      </c>
+      <c r="E163" s="2">
+        <v>45676.5625</v>
+      </c>
+      <c r="F163">
+        <v>18</v>
+      </c>
+      <c r="G163" t="s">
+        <v>84</v>
+      </c>
+      <c r="H163" t="s">
+        <v>74</v>
+      </c>
+      <c r="I163">
+        <v>0</v>
+      </c>
+      <c r="J163">
+        <v>2</v>
+      </c>
+      <c r="K163">
+        <v>2</v>
+      </c>
+      <c r="L163">
+        <v>0</v>
+      </c>
+      <c r="M163">
+        <v>2</v>
+      </c>
+      <c r="N163">
+        <v>2</v>
+      </c>
+      <c r="O163" t="s">
+        <v>96</v>
+      </c>
+      <c r="P163" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q163">
+        <v>2.38</v>
+      </c>
+      <c r="R163">
+        <v>2.25</v>
+      </c>
+      <c r="S163">
+        <v>4.75</v>
+      </c>
+      <c r="T163">
+        <v>1.36</v>
+      </c>
+      <c r="U163">
+        <v>3</v>
+      </c>
+      <c r="V163">
+        <v>2.63</v>
+      </c>
+      <c r="W163">
+        <v>1.44</v>
+      </c>
+      <c r="X163">
+        <v>7</v>
+      </c>
+      <c r="Y163">
+        <v>1.1</v>
+      </c>
+      <c r="Z163">
+        <v>1.85</v>
+      </c>
+      <c r="AA163">
+        <v>4</v>
+      </c>
+      <c r="AB163">
+        <v>3.75</v>
+      </c>
+      <c r="AC163">
+        <v>1.03</v>
+      </c>
+      <c r="AD163">
+        <v>13</v>
+      </c>
+      <c r="AE163">
+        <v>1.25</v>
+      </c>
+      <c r="AF163">
+        <v>4</v>
+      </c>
+      <c r="AG163">
+        <v>1.81</v>
+      </c>
+      <c r="AH163">
+        <v>2</v>
+      </c>
+      <c r="AI163">
+        <v>1.75</v>
+      </c>
+      <c r="AJ163">
+        <v>2</v>
+      </c>
+      <c r="AK163">
+        <v>1.21</v>
+      </c>
+      <c r="AL163">
+        <v>1.25</v>
+      </c>
+      <c r="AM163">
+        <v>2</v>
+      </c>
+      <c r="AN163">
+        <v>1.25</v>
+      </c>
+      <c r="AO163">
+        <v>0.63</v>
+      </c>
+      <c r="AP163">
+        <v>1.11</v>
+      </c>
+      <c r="AQ163">
+        <v>0.89</v>
+      </c>
+      <c r="AR163">
+        <v>1.3</v>
+      </c>
+      <c r="AS163">
+        <v>1.04</v>
+      </c>
+      <c r="AT163">
+        <v>2.34</v>
+      </c>
+      <c r="AU163">
+        <v>3</v>
+      </c>
+      <c r="AV163">
+        <v>5</v>
+      </c>
+      <c r="AW163">
+        <v>16</v>
+      </c>
+      <c r="AX163">
+        <v>5</v>
+      </c>
+      <c r="AY163">
+        <v>27</v>
+      </c>
+      <c r="AZ163">
+        <v>10</v>
+      </c>
+      <c r="BA163">
+        <v>6</v>
+      </c>
+      <c r="BB163">
+        <v>2</v>
+      </c>
+      <c r="BC163">
+        <v>8</v>
+      </c>
+      <c r="BD163">
+        <v>1.65</v>
+      </c>
+      <c r="BE163">
+        <v>6.5</v>
+      </c>
+      <c r="BF163">
+        <v>2.48</v>
+      </c>
+      <c r="BG163">
+        <v>1.3</v>
+      </c>
+      <c r="BH163">
+        <v>3.15</v>
+      </c>
+      <c r="BI163">
+        <v>1.52</v>
+      </c>
+      <c r="BJ163">
+        <v>2.32</v>
+      </c>
+      <c r="BK163">
+        <v>1.86</v>
+      </c>
+      <c r="BL163">
+        <v>1.82</v>
+      </c>
+      <c r="BM163">
+        <v>2.35</v>
+      </c>
+      <c r="BN163">
+        <v>1.5</v>
+      </c>
+      <c r="BO163">
+        <v>3.05</v>
+      </c>
+      <c r="BP163">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Germany Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Germany Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="306">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -631,6 +631,9 @@
     <t>['1', '24']</t>
   </si>
   <si>
+    <t>['50', '53']</t>
+  </si>
+  <si>
     <t>['12', '38', '90+11']</t>
   </si>
   <si>
@@ -926,6 +929,9 @@
   </si>
   <si>
     <t>['5', '45+1']</t>
+  </si>
+  <si>
+    <t>['13', '80']</t>
   </si>
 </sst>
 </file>
@@ -1287,7 +1293,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP163"/>
+  <dimension ref="A1:BP164"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1543,7 +1549,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q2">
         <v>4.75</v>
@@ -1955,7 +1961,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2036,7 +2042,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ4">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2161,7 +2167,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q5">
         <v>3.75</v>
@@ -2367,7 +2373,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2573,7 +2579,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2985,7 +2991,7 @@
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q9">
         <v>5.5</v>
@@ -3063,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ9">
         <v>2.22</v>
@@ -3191,7 +3197,7 @@
         <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q10">
         <v>2.75</v>
@@ -3603,7 +3609,7 @@
         <v>98</v>
       </c>
       <c r="P12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3809,7 +3815,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q13">
         <v>3.6</v>
@@ -4015,7 +4021,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4221,7 +4227,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q15">
         <v>3</v>
@@ -4633,7 +4639,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -5251,7 +5257,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
@@ -5663,7 +5669,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q22">
         <v>4.75</v>
@@ -6075,7 +6081,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q24">
         <v>3.2</v>
@@ -6153,7 +6159,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ24">
         <v>1.78</v>
@@ -6281,7 +6287,7 @@
         <v>107</v>
       </c>
       <c r="P25" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q25">
         <v>3.1</v>
@@ -6487,7 +6493,7 @@
         <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q26">
         <v>7.5</v>
@@ -6693,7 +6699,7 @@
         <v>109</v>
       </c>
       <c r="P27" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q27">
         <v>2.63</v>
@@ -6899,7 +6905,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7105,7 +7111,7 @@
         <v>110</v>
       </c>
       <c r="P29" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -7311,7 +7317,7 @@
         <v>96</v>
       </c>
       <c r="P30" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -7517,7 +7523,7 @@
         <v>96</v>
       </c>
       <c r="P31" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q31">
         <v>5.5</v>
@@ -7723,7 +7729,7 @@
         <v>111</v>
       </c>
       <c r="P32" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q32">
         <v>2.63</v>
@@ -7929,7 +7935,7 @@
         <v>112</v>
       </c>
       <c r="P33" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -8010,7 +8016,7 @@
         <v>1</v>
       </c>
       <c r="AQ33">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR33">
         <v>1.57</v>
@@ -8341,7 +8347,7 @@
         <v>114</v>
       </c>
       <c r="P35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q35">
         <v>1.73</v>
@@ -8959,7 +8965,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q38">
         <v>1.62</v>
@@ -9371,7 +9377,7 @@
         <v>96</v>
       </c>
       <c r="P40" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9577,7 +9583,7 @@
         <v>118</v>
       </c>
       <c r="P41" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q41">
         <v>3.5</v>
@@ -9655,7 +9661,7 @@
         <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ41">
         <v>1.5</v>
@@ -9783,7 +9789,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q42">
         <v>2.2</v>
@@ -10195,7 +10201,7 @@
         <v>120</v>
       </c>
       <c r="P44" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10401,7 +10407,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q45">
         <v>4.5</v>
@@ -10607,7 +10613,7 @@
         <v>122</v>
       </c>
       <c r="P46" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q46">
         <v>2.75</v>
@@ -11019,7 +11025,7 @@
         <v>124</v>
       </c>
       <c r="P48" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q48">
         <v>1.36</v>
@@ -11100,7 +11106,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ48">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR48">
         <v>2.42</v>
@@ -11431,7 +11437,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q50">
         <v>3.6</v>
@@ -11637,7 +11643,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q51">
         <v>3.4</v>
@@ -11843,7 +11849,7 @@
         <v>96</v>
       </c>
       <c r="P52" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12255,7 +12261,7 @@
         <v>127</v>
       </c>
       <c r="P54" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q54">
         <v>5</v>
@@ -12461,7 +12467,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q55">
         <v>1.67</v>
@@ -12667,7 +12673,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q56">
         <v>1.67</v>
@@ -12873,7 +12879,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q57">
         <v>1.83</v>
@@ -13285,7 +13291,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13491,7 +13497,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q60">
         <v>4.33</v>
@@ -13697,7 +13703,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14109,7 +14115,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14315,7 +14321,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q64">
         <v>2.75</v>
@@ -14393,7 +14399,7 @@
         <v>2.33</v>
       </c>
       <c r="AP64">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ64">
         <v>1.78</v>
@@ -14521,7 +14527,7 @@
         <v>136</v>
       </c>
       <c r="P65" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q65">
         <v>2.6</v>
@@ -14727,7 +14733,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -15139,7 +15145,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15426,7 +15432,7 @@
         <v>2</v>
       </c>
       <c r="AQ69">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR69">
         <v>2.2</v>
@@ -15551,7 +15557,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q70">
         <v>4.5</v>
@@ -15757,7 +15763,7 @@
         <v>96</v>
       </c>
       <c r="P71" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q71">
         <v>7</v>
@@ -15963,7 +15969,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16787,7 +16793,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q76">
         <v>1.73</v>
@@ -16993,7 +16999,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -17483,7 +17489,7 @@
         <v>0</v>
       </c>
       <c r="AP79">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ79">
         <v>0.89</v>
@@ -18435,7 +18441,7 @@
         <v>96</v>
       </c>
       <c r="P84" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18722,7 +18728,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ85">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR85">
         <v>0.97</v>
@@ -18847,7 +18853,7 @@
         <v>148</v>
       </c>
       <c r="P86" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q86">
         <v>3.6</v>
@@ -19053,7 +19059,7 @@
         <v>149</v>
       </c>
       <c r="P87" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q87">
         <v>7</v>
@@ -19671,7 +19677,7 @@
         <v>150</v>
       </c>
       <c r="P90" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19877,7 +19883,7 @@
         <v>151</v>
       </c>
       <c r="P91" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q91">
         <v>3.25</v>
@@ -20289,7 +20295,7 @@
         <v>153</v>
       </c>
       <c r="P93" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q93">
         <v>1.53</v>
@@ -20907,7 +20913,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21191,7 +21197,7 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ97">
         <v>0.5600000000000001</v>
@@ -21525,7 +21531,7 @@
         <v>96</v>
       </c>
       <c r="P99" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -21937,7 +21943,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22018,7 +22024,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ101">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR101">
         <v>1.26</v>
@@ -22143,7 +22149,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q102">
         <v>4.75</v>
@@ -22349,7 +22355,7 @@
         <v>162</v>
       </c>
       <c r="P103" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q103">
         <v>2.5</v>
@@ -22761,7 +22767,7 @@
         <v>108</v>
       </c>
       <c r="P105" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q105">
         <v>2.2</v>
@@ -22967,7 +22973,7 @@
         <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q106">
         <v>3.4</v>
@@ -23173,7 +23179,7 @@
         <v>107</v>
       </c>
       <c r="P107" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23585,7 +23591,7 @@
         <v>96</v>
       </c>
       <c r="P109" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -23791,7 +23797,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -23997,7 +24003,7 @@
         <v>96</v>
       </c>
       <c r="P111" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q111">
         <v>4.75</v>
@@ -24203,7 +24209,7 @@
         <v>96</v>
       </c>
       <c r="P112" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q112">
         <v>3.4</v>
@@ -24409,7 +24415,7 @@
         <v>167</v>
       </c>
       <c r="P113" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q113">
         <v>2.05</v>
@@ -24615,7 +24621,7 @@
         <v>168</v>
       </c>
       <c r="P114" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q114">
         <v>1.4</v>
@@ -25027,7 +25033,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -25233,7 +25239,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25311,7 +25317,7 @@
         <v>2.2</v>
       </c>
       <c r="AP117">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ117">
         <v>1.56</v>
@@ -25439,7 +25445,7 @@
         <v>171</v>
       </c>
       <c r="P118" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25645,7 +25651,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q119">
         <v>2.75</v>
@@ -25851,7 +25857,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q120">
         <v>2.2</v>
@@ -26057,7 +26063,7 @@
         <v>174</v>
       </c>
       <c r="P121" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q121">
         <v>5.5</v>
@@ -26263,7 +26269,7 @@
         <v>96</v>
       </c>
       <c r="P122" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q122">
         <v>5.5</v>
@@ -26469,7 +26475,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q123">
         <v>1.91</v>
@@ -26550,7 +26556,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ123">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR123">
         <v>1.56</v>
@@ -26675,7 +26681,7 @@
         <v>96</v>
       </c>
       <c r="P124" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26881,7 +26887,7 @@
         <v>176</v>
       </c>
       <c r="P125" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q125">
         <v>4.33</v>
@@ -27087,7 +27093,7 @@
         <v>177</v>
       </c>
       <c r="P126" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q126">
         <v>1.83</v>
@@ -27293,7 +27299,7 @@
         <v>178</v>
       </c>
       <c r="P127" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q127">
         <v>2.63</v>
@@ -27499,7 +27505,7 @@
         <v>179</v>
       </c>
       <c r="P128" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q128">
         <v>1.73</v>
@@ -27705,7 +27711,7 @@
         <v>180</v>
       </c>
       <c r="P129" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q129">
         <v>3.5</v>
@@ -27911,7 +27917,7 @@
         <v>96</v>
       </c>
       <c r="P130" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q130">
         <v>2</v>
@@ -28117,7 +28123,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q131">
         <v>2.4</v>
@@ -28323,7 +28329,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28529,7 +28535,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -29147,7 +29153,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29225,7 +29231,7 @@
         <v>0.33</v>
       </c>
       <c r="AP136">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ136">
         <v>0.5600000000000001</v>
@@ -29353,7 +29359,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q137">
         <v>3.2</v>
@@ -29971,7 +29977,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q140">
         <v>1.83</v>
@@ -30052,7 +30058,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ140">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR140">
         <v>1.59</v>
@@ -30383,7 +30389,7 @@
         <v>96</v>
       </c>
       <c r="P142" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q142">
         <v>4</v>
@@ -30589,7 +30595,7 @@
         <v>96</v>
       </c>
       <c r="P143" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -30795,7 +30801,7 @@
         <v>190</v>
       </c>
       <c r="P144" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31001,7 +31007,7 @@
         <v>96</v>
       </c>
       <c r="P145" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31207,7 +31213,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q146">
         <v>5.5</v>
@@ -31697,7 +31703,7 @@
         <v>1.14</v>
       </c>
       <c r="AP148">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ148">
         <v>0.89</v>
@@ -32237,7 +32243,7 @@
         <v>195</v>
       </c>
       <c r="P151" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q151">
         <v>2.6</v>
@@ -32649,7 +32655,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -32855,7 +32861,7 @@
         <v>96</v>
       </c>
       <c r="P154" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33267,7 +33273,7 @@
         <v>199</v>
       </c>
       <c r="P156" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q156">
         <v>3.4</v>
@@ -33473,7 +33479,7 @@
         <v>200</v>
       </c>
       <c r="P157" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33679,7 +33685,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q158">
         <v>3.2</v>
@@ -34091,7 +34097,7 @@
         <v>202</v>
       </c>
       <c r="P160" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q160">
         <v>1.53</v>
@@ -34297,7 +34303,7 @@
         <v>203</v>
       </c>
       <c r="P161" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q161">
         <v>1.73</v>
@@ -34503,7 +34509,7 @@
         <v>204</v>
       </c>
       <c r="P162" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q162">
         <v>3.25</v>
@@ -34709,7 +34715,7 @@
         <v>96</v>
       </c>
       <c r="P163" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q163">
         <v>2.38</v>
@@ -34866,6 +34872,212 @@
       </c>
       <c r="BP163">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="164" spans="1:68">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>7491981</v>
+      </c>
+      <c r="C164" t="s">
+        <v>68</v>
+      </c>
+      <c r="D164" t="s">
+        <v>69</v>
+      </c>
+      <c r="E164" s="2">
+        <v>45681.6875</v>
+      </c>
+      <c r="F164">
+        <v>19</v>
+      </c>
+      <c r="G164" t="s">
+        <v>77</v>
+      </c>
+      <c r="H164" t="s">
+        <v>81</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+      <c r="J164">
+        <v>1</v>
+      </c>
+      <c r="K164">
+        <v>1</v>
+      </c>
+      <c r="L164">
+        <v>2</v>
+      </c>
+      <c r="M164">
+        <v>2</v>
+      </c>
+      <c r="N164">
+        <v>4</v>
+      </c>
+      <c r="O164" t="s">
+        <v>205</v>
+      </c>
+      <c r="P164" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q164">
+        <v>1.91</v>
+      </c>
+      <c r="R164">
+        <v>2.5</v>
+      </c>
+      <c r="S164">
+        <v>6</v>
+      </c>
+      <c r="T164">
+        <v>1.29</v>
+      </c>
+      <c r="U164">
+        <v>3.5</v>
+      </c>
+      <c r="V164">
+        <v>2.25</v>
+      </c>
+      <c r="W164">
+        <v>1.57</v>
+      </c>
+      <c r="X164">
+        <v>5.5</v>
+      </c>
+      <c r="Y164">
+        <v>1.14</v>
+      </c>
+      <c r="Z164">
+        <v>1.49</v>
+      </c>
+      <c r="AA164">
+        <v>4.8</v>
+      </c>
+      <c r="AB164">
+        <v>6.5</v>
+      </c>
+      <c r="AC164">
+        <v>1.02</v>
+      </c>
+      <c r="AD164">
+        <v>19</v>
+      </c>
+      <c r="AE164">
+        <v>1.19</v>
+      </c>
+      <c r="AF164">
+        <v>4.75</v>
+      </c>
+      <c r="AG164">
+        <v>1.57</v>
+      </c>
+      <c r="AH164">
+        <v>2.25</v>
+      </c>
+      <c r="AI164">
+        <v>1.75</v>
+      </c>
+      <c r="AJ164">
+        <v>2</v>
+      </c>
+      <c r="AK164">
+        <v>1.12</v>
+      </c>
+      <c r="AL164">
+        <v>1.2</v>
+      </c>
+      <c r="AM164">
+        <v>2.55</v>
+      </c>
+      <c r="AN164">
+        <v>1.22</v>
+      </c>
+      <c r="AO164">
+        <v>0.25</v>
+      </c>
+      <c r="AP164">
+        <v>1.2</v>
+      </c>
+      <c r="AQ164">
+        <v>0.33</v>
+      </c>
+      <c r="AR164">
+        <v>1.34</v>
+      </c>
+      <c r="AS164">
+        <v>1.19</v>
+      </c>
+      <c r="AT164">
+        <v>2.53</v>
+      </c>
+      <c r="AU164">
+        <v>6</v>
+      </c>
+      <c r="AV164">
+        <v>3</v>
+      </c>
+      <c r="AW164">
+        <v>17</v>
+      </c>
+      <c r="AX164">
+        <v>3</v>
+      </c>
+      <c r="AY164">
+        <v>29</v>
+      </c>
+      <c r="AZ164">
+        <v>8</v>
+      </c>
+      <c r="BA164">
+        <v>10</v>
+      </c>
+      <c r="BB164">
+        <v>3</v>
+      </c>
+      <c r="BC164">
+        <v>13</v>
+      </c>
+      <c r="BD164">
+        <v>1.25</v>
+      </c>
+      <c r="BE164">
+        <v>7.6</v>
+      </c>
+      <c r="BF164">
+        <v>5.1</v>
+      </c>
+      <c r="BG164">
+        <v>1.19</v>
+      </c>
+      <c r="BH164">
+        <v>3.82</v>
+      </c>
+      <c r="BI164">
+        <v>1.39</v>
+      </c>
+      <c r="BJ164">
+        <v>2.67</v>
+      </c>
+      <c r="BK164">
+        <v>1.7</v>
+      </c>
+      <c r="BL164">
+        <v>2.03</v>
+      </c>
+      <c r="BM164">
+        <v>2.12</v>
+      </c>
+      <c r="BN164">
+        <v>1.61</v>
+      </c>
+      <c r="BO164">
+        <v>2.74</v>
+      </c>
+      <c r="BP164">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>
